--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO26"/>
+  <dimension ref="A1:AO62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -930,27 +930,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -971,13 +971,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>6.79</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>45894.4375</v>
+        <v>45894.375</v>
       </c>
     </row>
     <row r="5">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1635,12 +1635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>45894.45833333334</v>
+        <v>45894.4375</v>
       </c>
     </row>
     <row r="10">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1853,10 +1853,10 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>45894.54166666666</v>
+        <v>45894.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1917,27 +1917,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
-        <v>45894.5625</v>
+        <v>45894.47916666666</v>
       </c>
     </row>
     <row r="12">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="AO12" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.5</v>
       </c>
     </row>
     <row r="13">
@@ -2199,27 +2199,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2331,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="AO13" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.5</v>
       </c>
     </row>
     <row r="14">
@@ -2340,27 +2340,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2472,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.5</v>
       </c>
     </row>
     <row r="15">
@@ -2481,27 +2481,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="AO15" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.5</v>
       </c>
     </row>
     <row r="16">
@@ -2622,27 +2622,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="AO16" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.52083333334</v>
       </c>
     </row>
     <row r="17">
@@ -2763,27 +2763,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="AO17" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.53125</v>
       </c>
     </row>
     <row r="18">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3036,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="AO18" s="3" t="n">
-        <v>45894.60416666666</v>
+        <v>45894.53125</v>
       </c>
     </row>
     <row r="19">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="AO19" s="3" t="n">
-        <v>45894.60416666666</v>
+        <v>45894.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -3186,27 +3186,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="AO20" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.54166666666</v>
       </c>
     </row>
     <row r="21">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="AO21" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.54166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="AO22" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.5625</v>
       </c>
     </row>
     <row r="23">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="AO23" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.5625</v>
       </c>
     </row>
     <row r="24">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="AO24" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.5625</v>
       </c>
     </row>
     <row r="25">
@@ -3891,27 +3891,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="AO25" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="26">
@@ -4032,139 +4032,5215 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sarpsborg 08</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="3" t="n">
+        <v>45894.58333333334</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Wisła Płock</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Zagłębie Lubin</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="3" t="n">
+        <v>45894.58333333334</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Falkenberg</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3" t="n">
+        <v>45894.58333333334</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>GAIS</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mjällby</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3" t="n">
+        <v>45894.58333333334</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3" t="n">
+        <v>45894.58333333334</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Öster</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3" t="n">
+        <v>45894.58333333334</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Denmark Superliga</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Nordsjælland</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Viborg</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3" t="n">
+        <v>45894.58333333334</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Poland 1. Liga</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Tychy 71</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Stal Mielec</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" s="3" t="n">
+        <v>45894.58333333334</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Trelleborg</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Landskrona</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3" t="n">
+        <v>45894.58333333334</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Athletic Club Bilbao</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" s="3" t="n">
+        <v>45894.60416666666</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Israel Israeli Premier League</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Bnei Sakhnin</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Beitar Jerusalem</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="3" t="n">
+        <v>45894.60416666666</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Albacete Balompié</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" s="3" t="n">
+        <v>45894.60416666666</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Utrecht II</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ajax II</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" s="3" t="n">
+        <v>45894.625</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Petrojet</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Al Mokawloon</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="3" t="n">
+        <v>45894.625</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AZ II</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" s="3" t="n">
+        <v>45894.625</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Stjarnan</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" s="3" t="n">
+        <v>45894.625</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Pyramids FC</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3" t="n">
+        <v>45894.625</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Switzerland Challenge League</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aarau</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Stade Lausanne-Ouchy</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" s="3" t="n">
+        <v>45894.63541666666</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Switzerland Challenge League</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Neuchâtel Xamax</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vaduz</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" s="3" t="n">
+        <v>45894.63541666666</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Turkey Süper Lig</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Eyüpspor</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Alanyaspor</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" s="3" t="n">
+        <v>45894.64583333334</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Turkey 1. Lig</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>İstanbulspor</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Manisa BBSK</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="3" t="n">
+        <v>45894.64583333334</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Sampdoria</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO47" s="3" t="n">
+        <v>45894.64583333334</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Novara</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Inter II</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO48" s="3" t="n">
+        <v>45894.64583333334</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Inter Milan</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M49" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N49" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO49" s="3" t="n">
+        <v>45894.65625</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group C</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Crotone</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Benevento</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3" t="n">
+        <v>45894.66666666666</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Newcastle United</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3" t="n">
+        <v>45894.66666666666</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group C</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Casertana</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Team Altamura</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="3" t="n">
+        <v>45894.66666666666</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3" t="n">
+        <v>45894.67708333334</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Afturelding</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO54" s="3" t="n">
+        <v>45894.67708333334</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Spain Segunda División</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Córdoba</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>UD Las Palmas</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" s="3" t="n">
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="3" t="n">
         <v>45894.6875</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Sevilla FC</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Getafe CF</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO56" s="3" t="n">
+        <v>45894.6875</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N57" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W57" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO57" s="3" t="n">
+        <v>45894.79166666666</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M58" t="n">
+        <v>5</v>
+      </c>
+      <c r="N58" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="3" t="n">
+        <v>45894.79166666666</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO59" s="3" t="n">
+        <v>45894.83333333334</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Delfin SC</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO60" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M61" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N61" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO61" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N62" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO62" s="3" t="n">
+        <v>45894.89583333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO62"/>
+  <dimension ref="A1:AO64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,22 +3050,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3191,22 +3191,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,10 +3404,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,46 +3509,46 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
         <v>2.13</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>4.06</v>
+        <v>3.85</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,22 +5165,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,10 +5378,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5856,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="AO38" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="39">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6429,27 +6429,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6561,7 +6561,7 @@
         <v>0</v>
       </c>
       <c r="AO43" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="44">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6843,7 +6843,7 @@
         <v>0</v>
       </c>
       <c r="AO45" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="46">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7275,12 +7275,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="AO49" s="3" t="n">
-        <v>45894.65625</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="50">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7548,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="AO50" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.65625</v>
       </c>
     </row>
     <row r="51">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7634,16 +7634,16 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7775,16 +7775,16 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
@@ -7839,12 +7839,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7971,7 +7971,7 @@
         <v>0</v>
       </c>
       <c r="AO53" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="54">
@@ -7985,22 +7985,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8121,27 +8121,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8253,7 +8253,7 @@
         <v>0</v>
       </c>
       <c r="AO55" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="56">
@@ -8403,27 +8403,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8474,10 +8474,10 @@
         <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
         <v>0</v>
@@ -8535,7 +8535,7 @@
         <v>0</v>
       </c>
       <c r="AO57" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="58">
@@ -8544,27 +8544,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.27</v>
+        <v>2.29</v>
       </c>
       <c r="M58" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="N58" t="n">
-        <v>10.5</v>
+        <v>3.52</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8621,10 +8621,10 @@
         <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="Y58" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -8676,7 +8676,7 @@
         <v>0</v>
       </c>
       <c r="AO58" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="59">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8762,10 +8762,10 @@
         <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z59" t="n">
         <v>0</v>
@@ -8817,7 +8817,7 @@
         <v>0</v>
       </c>
       <c r="AO59" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="60">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="M60" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N60" t="n">
-        <v>3.95</v>
+        <v>2.7</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8897,16 +8897,16 @@
         <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="X60" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
         <v>0</v>
@@ -8958,7 +8958,7 @@
         <v>0</v>
       </c>
       <c r="AO60" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="61">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9044,10 +9044,10 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -9099,7 +9099,7 @@
         <v>0</v>
       </c>
       <c r="AO61" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.83333333334</v>
       </c>
     </row>
     <row r="62">
@@ -9108,138 +9108,420 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M62" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N62" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO62" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Delfin SC</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M63" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr">
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L62" t="n">
+      <c r="L64" t="n">
         <v>1.64</v>
       </c>
-      <c r="M62" t="n">
+      <c r="M64" t="n">
         <v>3.35</v>
       </c>
-      <c r="N62" t="n">
+      <c r="N64" t="n">
         <v>5.2</v>
       </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
         <v>2.18</v>
       </c>
-      <c r="Y62" t="n">
+      <c r="Y64" t="n">
         <v>1.58</v>
       </c>
-      <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO62" s="3" t="n">
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3" t="n">
         <v>45894.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO64"/>
+  <dimension ref="A1:AO66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1853,10 +1853,10 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2564,10 +2564,10 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -3050,22 +3050,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>4.06</v>
+        <v>3.85</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4397,10 +4397,10 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,16 +4532,16 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5165,22 +5165,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,10 +5378,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.1</v>
+        <v>1.77</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>1.73</v>
+        <v>4.6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5519,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.97</v>
+        <v>1.61</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="AO39" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="40">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6702,7 +6702,7 @@
         <v>0</v>
       </c>
       <c r="AO44" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="45">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6984,7 +6984,7 @@
         <v>0</v>
       </c>
       <c r="AO46" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="47">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="M48" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7211,10 +7211,10 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7548,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="AO50" s="3" t="n">
-        <v>45894.65625</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="51">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7634,10 +7634,10 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -7689,7 +7689,7 @@
         <v>0</v>
       </c>
       <c r="AO51" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.65625</v>
       </c>
     </row>
     <row r="52">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7775,16 +7775,16 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7916,16 +7916,16 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
@@ -7980,12 +7980,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8112,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="AO54" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="55">
@@ -8126,22 +8126,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8262,27 +8262,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8394,7 +8394,7 @@
         <v>0</v>
       </c>
       <c r="AO56" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="57">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8480,10 +8480,10 @@
         <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z57" t="n">
         <v>0</v>
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8621,10 +8621,10 @@
         <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -8685,27 +8685,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8762,10 +8762,10 @@
         <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
         <v>0</v>
@@ -8817,7 +8817,7 @@
         <v>0</v>
       </c>
       <c r="AO59" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="60">
@@ -8826,27 +8826,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8897,10 +8897,10 @@
         <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
         <v>0</v>
@@ -8958,7 +8958,7 @@
         <v>0</v>
       </c>
       <c r="AO60" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="61">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X61" t="n">
         <v>0</v>
@@ -9099,7 +9099,7 @@
         <v>0</v>
       </c>
       <c r="AO61" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="62">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="M62" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="N62" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -9240,7 +9240,7 @@
         <v>0</v>
       </c>
       <c r="AO62" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="63">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9326,10 +9326,10 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -9381,7 +9381,7 @@
         <v>0</v>
       </c>
       <c r="AO63" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.83333333334</v>
       </c>
     </row>
     <row r="64">
@@ -9390,138 +9390,420 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M64" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N64" t="n">
+        <v>12</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Delfin SC</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr">
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L64" t="n">
+      <c r="L66" t="n">
         <v>1.64</v>
       </c>
-      <c r="M64" t="n">
+      <c r="M66" t="n">
         <v>3.35</v>
       </c>
-      <c r="N64" t="n">
+      <c r="N66" t="n">
         <v>5.2</v>
       </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" t="n">
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
         <v>2.18</v>
       </c>
-      <c r="Y64" t="n">
+      <c r="Y66" t="n">
         <v>1.58</v>
       </c>
-      <c r="Z64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO64" s="3" t="n">
+      <c r="Z66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO66" s="3" t="n">
         <v>45894.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2423,10 +2423,10 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2564,10 +2564,10 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3191,22 +3191,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,16 +3263,16 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,16 +4391,16 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,16 +4532,16 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5165,22 +5165,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5237,16 +5237,16 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,10 +5378,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5519,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.1</v>
+        <v>1.77</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>1.73</v>
+        <v>4.6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.97</v>
+        <v>1.61</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6011,22 +6011,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7211,10 +7211,10 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8126,22 +8126,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8267,22 +8267,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8480,10 +8480,10 @@
         <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
         <v>0</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8762,10 +8762,10 @@
         <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z59" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G60" t="n">

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2282,10 +2282,10 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2423,10 +2423,10 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3191,22 +3191,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,16 +3263,16 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4115,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,16 +4250,16 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,22 +5165,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5237,16 +5237,16 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,10 +5378,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -6011,22 +6011,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7775,16 +7775,16 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7916,16 +7916,16 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8480,10 +8480,10 @@
         <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z57" t="n">
         <v>0</v>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8762,10 +8762,10 @@
         <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.28</v>
+        <v>1.85</v>
       </c>
       <c r="M64" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>12</v>
+        <v>3.95</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9467,10 +9467,10 @@
         <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.85</v>
+        <v>1.28</v>
       </c>
       <c r="M65" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="N65" t="n">
-        <v>3.95</v>
+        <v>12</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9608,10 +9608,10 @@
         <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,22 +3050,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,16 +3122,16 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7775,16 +7775,16 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7916,16 +7916,16 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.85</v>
+        <v>1.28</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="N64" t="n">
-        <v>3.95</v>
+        <v>12</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9467,10 +9467,10 @@
         <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.28</v>
+        <v>1.85</v>
       </c>
       <c r="M65" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="N65" t="n">
-        <v>12</v>
+        <v>3.95</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9608,10 +9608,10 @@
         <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2282,10 +2282,10 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2564,10 +2564,10 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -3050,22 +3050,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,16 +3122,16 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3191,22 +3191,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,16 +3263,16 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,10 +3404,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4115,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,16 +4250,16 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,16 +4391,16 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,16 +4955,16 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.1</v>
+        <v>1.77</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>1.73</v>
+        <v>4.6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.97</v>
+        <v>1.61</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7916,16 +7916,16 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8057,16 +8057,16 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB54" t="n">
         <v>0</v>
@@ -8126,22 +8126,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8267,22 +8267,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8480,10 +8480,10 @@
         <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
         <v>0</v>
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8903,10 +8903,10 @@
         <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z60" t="n">
         <v>0</v>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.7</v>
+        <v>1.27</v>
       </c>
       <c r="M61" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="N61" t="n">
-        <v>2.95</v>
+        <v>10.5</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9038,16 +9038,16 @@
         <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.27</v>
+        <v>2.7</v>
       </c>
       <c r="M62" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="N62" t="n">
-        <v>10.5</v>
+        <v>2.95</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9179,16 +9179,16 @@
         <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X62" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.28</v>
+        <v>1.85</v>
       </c>
       <c r="M64" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>12</v>
+        <v>3.95</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9467,10 +9467,10 @@
         <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.85</v>
+        <v>1.28</v>
       </c>
       <c r="M65" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="N65" t="n">
-        <v>3.95</v>
+        <v>12</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9608,10 +9608,10 @@
         <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO66"/>
+  <dimension ref="A1:AO68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2564,10 +2564,10 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,22 +3050,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,16 +3122,16 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3191,22 +3191,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,16 +3263,16 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,10 +3404,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4256,10 +4256,10 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4397,10 +4397,10 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,16 +4673,16 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,16 +4955,16 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5301,27 +5301,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5433,7 +5433,7 @@
         <v>0</v>
       </c>
       <c r="AO35" s="3" t="n">
-        <v>45894.60416666666</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="36">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5519,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.1</v>
+        <v>1.77</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>1.73</v>
+        <v>4.6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.97</v>
+        <v>1.61</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -6006,12 +6006,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6138,7 +6138,7 @@
         <v>0</v>
       </c>
       <c r="AO40" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="41">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6843,7 +6843,7 @@
         <v>0</v>
       </c>
       <c r="AO45" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="46">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6993,12 +6993,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7125,7 +7125,7 @@
         <v>0</v>
       </c>
       <c r="AO47" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="48">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.42</v>
+        <v>2.35</v>
       </c>
       <c r="M51" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="N51" t="n">
-        <v>7.4</v>
+        <v>3.2</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7634,10 +7634,10 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -7689,7 +7689,7 @@
         <v>0</v>
       </c>
       <c r="AO51" s="3" t="n">
-        <v>45894.65625</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="52">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7775,10 +7775,10 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
@@ -7830,7 +7830,7 @@
         <v>0</v>
       </c>
       <c r="AO52" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.65625</v>
       </c>
     </row>
     <row r="53">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8253,7 +8253,7 @@
         <v>0</v>
       </c>
       <c r="AO55" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="56">
@@ -8267,22 +8267,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8403,27 +8403,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8535,7 +8535,7 @@
         <v>0</v>
       </c>
       <c r="AO57" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="58">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8903,10 +8903,10 @@
         <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
         <v>0</v>
@@ -8967,27 +8967,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.27</v>
+        <v>2.29</v>
       </c>
       <c r="M61" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="N61" t="n">
-        <v>10.5</v>
+        <v>3.52</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9044,10 +9044,10 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="Y61" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -9099,7 +9099,7 @@
         <v>0</v>
       </c>
       <c r="AO61" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="62">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.7</v>
+        <v>1.27</v>
       </c>
       <c r="M62" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="N62" t="n">
-        <v>2.95</v>
+        <v>10.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9179,16 +9179,16 @@
         <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -9249,12 +9249,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9320,10 +9320,10 @@
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X63" t="n">
         <v>0</v>
@@ -9381,7 +9381,7 @@
         <v>0</v>
       </c>
       <c r="AO63" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="64">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9467,10 +9467,10 @@
         <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -9522,7 +9522,7 @@
         <v>0</v>
       </c>
       <c r="AO64" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="65">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9608,10 +9608,10 @@
         <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
         <v>0</v>
       </c>
       <c r="AO65" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="66">
@@ -9672,138 +9672,420 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO66" s="3" t="n">
+        <v>45894.83333333334</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Delfin SC</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M67" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO67" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="inlineStr">
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L66" t="n">
+      <c r="L68" t="n">
         <v>1.64</v>
       </c>
-      <c r="M66" t="n">
+      <c r="M68" t="n">
         <v>3.35</v>
       </c>
-      <c r="N66" t="n">
+      <c r="N68" t="n">
         <v>5.2</v>
       </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="n">
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
         <v>2.18</v>
       </c>
-      <c r="Y66" t="n">
+      <c r="Y68" t="n">
         <v>1.58</v>
       </c>
-      <c r="Z66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO66" s="3" t="n">
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3" t="n">
         <v>45894.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO68"/>
+  <dimension ref="A1:AO73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -971,13 +971,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>5.22</v>
+        <v>5.8</v>
       </c>
       <c r="N4" t="n">
-        <v>6.79</v>
+        <v>9</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1013,10 +1013,10 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>3.74</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Z12" t="n">
         <v>2.35</v>
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -3050,22 +3050,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,16 +3122,16 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.83</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.27</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,16 +4250,16 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,16 +4391,16 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.2</v>
+        <v>1.54</v>
       </c>
       <c r="M30" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="N30" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,16 +4673,16 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5165,22 +5165,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,10 +5378,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N36" t="n">
-        <v>1.73</v>
+        <v>2.85</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5519,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6230,10 +6230,10 @@
         <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB41" t="n">
         <v>0</v>
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6984,7 +6984,7 @@
         <v>0</v>
       </c>
       <c r="AO46" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="47">
@@ -7134,12 +7134,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="AO48" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="49">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="AO49" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="50">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7634,10 +7634,10 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7775,10 +7775,10 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
@@ -7830,7 +7830,7 @@
         <v>0</v>
       </c>
       <c r="AO52" s="3" t="n">
-        <v>45894.65625</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="53">
@@ -7839,12 +7839,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7916,10 +7916,10 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -7971,7 +7971,7 @@
         <v>0</v>
       </c>
       <c r="AO53" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="54">
@@ -7980,12 +7980,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.6</v>
+        <v>1.42</v>
       </c>
       <c r="M54" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="N54" t="n">
-        <v>1.92</v>
+        <v>7.4</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8057,16 +8057,16 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="AO54" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.65625</v>
       </c>
     </row>
     <row r="55">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8394,7 +8394,7 @@
         <v>0</v>
       </c>
       <c r="AO56" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="57">
@@ -8403,27 +8403,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8535,7 +8535,7 @@
         <v>0</v>
       </c>
       <c r="AO57" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="58">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8621,16 +8621,16 @@
         <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB58" t="n">
         <v>0</v>
@@ -8676,7 +8676,7 @@
         <v>0</v>
       </c>
       <c r="AO58" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="59">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8817,7 +8817,7 @@
         <v>0</v>
       </c>
       <c r="AO59" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="60">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8903,10 +8903,10 @@
         <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z60" t="n">
         <v>0</v>
@@ -8958,7 +8958,7 @@
         <v>0</v>
       </c>
       <c r="AO60" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="61">
@@ -8967,27 +8967,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9044,10 +9044,10 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -9099,7 +9099,7 @@
         <v>0</v>
       </c>
       <c r="AO61" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="62">
@@ -9108,27 +9108,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.27</v>
+        <v>2.29</v>
       </c>
       <c r="M62" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="N62" t="n">
-        <v>10.5</v>
+        <v>3.52</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="Y62" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -9240,7 +9240,7 @@
         <v>0</v>
       </c>
       <c r="AO62" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="63">
@@ -9249,27 +9249,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="M63" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9320,16 +9320,16 @@
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -9381,7 +9381,7 @@
         <v>0</v>
       </c>
       <c r="AO63" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="64">
@@ -9390,27 +9390,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9522,7 +9522,7 @@
         <v>0</v>
       </c>
       <c r="AO64" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="65">
@@ -9531,27 +9531,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9663,7 +9663,7 @@
         <v>0</v>
       </c>
       <c r="AO65" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="66">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9743,10 +9743,10 @@
         <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X66" t="n">
         <v>0</v>
@@ -9804,7 +9804,7 @@
         <v>0</v>
       </c>
       <c r="AO66" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="67">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.85</v>
+        <v>1.32</v>
       </c>
       <c r="M67" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N67" t="n">
-        <v>3.95</v>
+        <v>7.8</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9890,10 +9890,10 @@
         <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>2.24</v>
+        <v>1.9</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -9945,7 +9945,7 @@
         <v>0</v>
       </c>
       <c r="AO67" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="68">
@@ -9954,138 +9954,843 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>CSA</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M68" t="n">
+        <v>3</v>
+      </c>
+      <c r="N68" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3" t="n">
+        <v>45894.8125</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Confiança</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M69" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N69" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3" t="n">
+        <v>45894.8125</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3" t="n">
+        <v>45894.83333333334</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M71" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N71" t="n">
+        <v>12</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Delfin SC</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M72" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N72" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO72" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="inlineStr">
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L68" t="n">
+      <c r="L73" t="n">
         <v>1.64</v>
       </c>
-      <c r="M68" t="n">
+      <c r="M73" t="n">
         <v>3.35</v>
       </c>
-      <c r="N68" t="n">
+      <c r="N73" t="n">
         <v>5.2</v>
       </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO68" s="3" t="n">
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3" t="n">
         <v>45894.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO73"/>
+  <dimension ref="A1:AO72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2135,16 +2135,16 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,16 +2558,16 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,22 +3050,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.83</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,16 +3122,16 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.13</v>
+        <v>2.43</v>
       </c>
       <c r="M25" t="n">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N26" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,16 +4109,16 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>1.72</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,10 +4250,10 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="M28" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,16 +4391,16 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.54</v>
+        <v>2.13</v>
       </c>
       <c r="M30" t="n">
-        <v>3.95</v>
+        <v>3.27</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6</v>
+        <v>2.91</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,16 +4673,16 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="N31" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.43</v>
+        <v>1.54</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N33" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,16 +5096,16 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5306,22 +5306,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="N35" t="n">
-        <v>2.79</v>
+        <v>3.19</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,10 +5378,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="M36" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.85</v>
+        <v>4.6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5519,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.77</v>
+        <v>4.1</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>4.6</v>
+        <v>1.73</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.61</v>
+        <v>1.97</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6230,10 +6230,10 @@
         <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6512,10 +6512,10 @@
         <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>6</v>
+        <v>2.35</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="N49" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="AO49" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="50">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7839,12 +7839,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.35</v>
+        <v>1.42</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="N53" t="n">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7916,10 +7916,10 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -7971,7 +7971,7 @@
         <v>0</v>
       </c>
       <c r="AO53" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.65625</v>
       </c>
     </row>
     <row r="54">
@@ -7980,12 +7980,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8057,10 +8057,10 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="AO54" s="3" t="n">
-        <v>45894.65625</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="55">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8480,16 +8480,16 @@
         <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB57" t="n">
         <v>0</v>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8621,16 +8621,16 @@
         <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
         <v>0</v>
@@ -8685,27 +8685,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8817,7 +8817,7 @@
         <v>0</v>
       </c>
       <c r="AO59" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="60">
@@ -8967,27 +8967,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9044,10 +9044,10 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -9099,7 +9099,7 @@
         <v>0</v>
       </c>
       <c r="AO61" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="62">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9326,10 +9326,10 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9467,10 +9467,10 @@
         <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -9531,27 +9531,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9608,10 +9608,10 @@
         <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
         <v>0</v>
       </c>
       <c r="AO65" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="66">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.32</v>
+        <v>2.12</v>
       </c>
       <c r="M67" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>7.8</v>
+        <v>3.5</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9890,10 +9890,10 @@
         <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -9945,7 +9945,7 @@
         <v>0</v>
       </c>
       <c r="AO67" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="68">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="M68" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>3.5</v>
+        <v>4.01</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10227,7 +10227,7 @@
         <v>0</v>
       </c>
       <c r="AO69" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.83333333334</v>
       </c>
     </row>
     <row r="70">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10313,10 +10313,10 @@
         <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AO70" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.875</v>
       </c>
     </row>
     <row r="71">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.28</v>
+        <v>1.85</v>
       </c>
       <c r="M71" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="N71" t="n">
-        <v>12</v>
+        <v>3.95</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="M72" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N72" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -10595,10 +10595,10 @@
         <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -10650,147 +10650,6 @@
         <v>0</v>
       </c>
       <c r="AO72" s="3" t="n">
-        <v>45894.875</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
-        <v>45894</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L73" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="M73" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N73" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" t="n">
-        <v>0</v>
-      </c>
-      <c r="W73" t="n">
-        <v>0</v>
-      </c>
-      <c r="X73" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO73" s="3" t="n">
         <v>45894.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2276,16 +2276,16 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,16 +2558,16 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -3050,22 +3050,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,16 +3122,16 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>3.27</v>
       </c>
       <c r="N26" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,16 +4109,16 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.72</v>
+        <v>2.22</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>3.21</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>2.79</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,10 +4250,10 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N28" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,16 +4391,16 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="M29" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="M30" t="n">
-        <v>3.27</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
-        <v>2.91</v>
+        <v>3.35</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="M31" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.95</v>
+        <v>3.28</v>
       </c>
       <c r="N33" t="n">
-        <v>4.6</v>
+        <v>3.19</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5102,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5165,22 +5165,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -5306,22 +5306,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="M35" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>3.19</v>
+        <v>2.7</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,10 +5378,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N40" t="n">
-        <v>1.73</v>
+        <v>2.85</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7634,10 +7634,10 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9044,10 +9044,10 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9326,10 +9326,10 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
       <c r="M65" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="N65" t="n">
-        <v>7.8</v>
+        <v>2.84</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9602,16 +9602,16 @@
         <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.6</v>
+        <v>1.32</v>
       </c>
       <c r="M66" t="n">
-        <v>2.61</v>
+        <v>4.3</v>
       </c>
       <c r="N66" t="n">
-        <v>2.84</v>
+        <v>7.8</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9743,16 +9743,16 @@
         <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z66" t="n">
         <v>0</v>
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N67" t="n">
-        <v>3.5</v>
+        <v>4.01</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
-        <v>4.01</v>
+        <v>3.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10241,7 +10241,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.28</v>
+        <v>1.85</v>
       </c>
       <c r="M70" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="N70" t="n">
-        <v>12</v>
+        <v>3.95</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10313,10 +10313,10 @@
         <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.85</v>
+        <v>1.28</v>
       </c>
       <c r="M71" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="N71" t="n">
-        <v>3.95</v>
+        <v>12</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO72"/>
+  <dimension ref="A1:AO73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.83</v>
+        <v>2.31</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N22" t="n">
-        <v>4.33</v>
+        <v>3.14</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3524,43 +3524,43 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X22" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="AO22" s="3" t="n">
-        <v>45894.5625</v>
+        <v>45894.54166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="AO25" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.5625</v>
       </c>
     </row>
     <row r="26">
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>3.27</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>2.91</v>
+        <v>3.35</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,10 +4250,10 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>3.65</v>
+        <v>2.85</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="M30" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="N31" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>3.19</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="M33" t="n">
-        <v>3.28</v>
+        <v>3.95</v>
       </c>
       <c r="N33" t="n">
-        <v>3.19</v>
+        <v>4.6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5102,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.43</v>
+        <v>2.13</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="N35" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,10 +5378,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -5442,27 +5442,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N36" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5519,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
@@ -5574,7 +5574,7 @@
         <v>0</v>
       </c>
       <c r="AO36" s="3" t="n">
-        <v>45894.60416666666</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="37">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6147,12 +6147,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="AO41" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="42">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6512,10 +6512,10 @@
         <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6857,22 +6857,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6935,10 +6935,10 @@
         <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
@@ -6993,12 +6993,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7125,7 +7125,7 @@
         <v>0</v>
       </c>
       <c r="AO47" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="48">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7407,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="AO49" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="50">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7634,10 +7634,10 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7775,10 +7775,10 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
@@ -7839,12 +7839,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7916,10 +7916,10 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -7971,7 +7971,7 @@
         <v>0</v>
       </c>
       <c r="AO53" s="3" t="n">
-        <v>45894.65625</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="54">
@@ -7980,12 +7980,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8057,10 +8057,10 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="AO54" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.65625</v>
       </c>
     </row>
     <row r="55">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8685,27 +8685,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8817,7 +8817,7 @@
         <v>0</v>
       </c>
       <c r="AO59" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="60">
@@ -8967,27 +8967,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9099,7 +9099,7 @@
         <v>0</v>
       </c>
       <c r="AO61" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="62">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="M63" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9326,10 +9326,10 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9467,10 +9467,10 @@
         <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -9531,27 +9531,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9602,10 +9602,10 @@
         <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
         <v>0</v>
       </c>
       <c r="AO65" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="66">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
       <c r="M66" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="N66" t="n">
-        <v>7.8</v>
+        <v>2.84</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9743,16 +9743,16 @@
         <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
         <v>0</v>
@@ -9813,12 +9813,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.87</v>
+        <v>1.32</v>
       </c>
       <c r="M67" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N67" t="n">
-        <v>4.01</v>
+        <v>7.8</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9890,10 +9890,10 @@
         <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -9945,7 +9945,7 @@
         <v>0</v>
       </c>
       <c r="AO67" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="68">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="M68" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>3.5</v>
+        <v>4.01</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10227,7 +10227,7 @@
         <v>0</v>
       </c>
       <c r="AO69" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="70">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10313,10 +10313,10 @@
         <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AO70" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.83333333334</v>
       </c>
     </row>
     <row r="71">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.28</v>
+        <v>1.85</v>
       </c>
       <c r="M71" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="N71" t="n">
-        <v>12</v>
+        <v>3.95</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -10518,138 +10518,279 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M72" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N72" t="n">
+        <v>12</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO72" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="inlineStr">
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L72" t="n">
+      <c r="L73" t="n">
         <v>1.64</v>
       </c>
-      <c r="M72" t="n">
+      <c r="M73" t="n">
         <v>3.35</v>
       </c>
-      <c r="N72" t="n">
+      <c r="N73" t="n">
         <v>5.2</v>
       </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" t="n">
-        <v>0</v>
-      </c>
-      <c r="X72" t="n">
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
         <v>2.1</v>
       </c>
-      <c r="Y72" t="n">
+      <c r="Y73" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO72" s="3" t="n">
+      <c r="Z73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3" t="n">
         <v>45894.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2135,16 +2135,16 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2276,16 +2276,16 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3101,43 +3101,43 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3524,43 +3524,43 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.83</v>
+        <v>2.47</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>4.33</v>
+        <v>2.93</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>3.74</v>
       </c>
       <c r="N26" t="n">
-        <v>3.35</v>
+        <v>3.89</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,16 +4250,16 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="M28" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>2.9</v>
+        <v>2.61</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,16 +4391,16 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="N29" t="n">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="N30" t="n">
-        <v>2.7</v>
+        <v>3.19</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="M32" t="n">
-        <v>3.28</v>
+        <v>3.01</v>
       </c>
       <c r="N32" t="n">
-        <v>3.19</v>
+        <v>2.78</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.54</v>
+        <v>2.22</v>
       </c>
       <c r="M33" t="n">
-        <v>3.95</v>
+        <v>3.21</v>
       </c>
       <c r="N33" t="n">
-        <v>4.6</v>
+        <v>2.79</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,16 +5096,16 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.06</v>
       </c>
       <c r="N34" t="n">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.13</v>
+        <v>1.54</v>
       </c>
       <c r="M35" t="n">
-        <v>3.27</v>
+        <v>3.95</v>
       </c>
       <c r="N35" t="n">
-        <v>2.91</v>
+        <v>4.6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,16 +5378,16 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -5447,22 +5447,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="M36" t="n">
-        <v>4</v>
+        <v>3.29</v>
       </c>
       <c r="N36" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5519,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.77</v>
+        <v>2.45</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
       <c r="N39" t="n">
-        <v>4.6</v>
+        <v>2.74</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6857,22 +6857,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6935,10 +6935,10 @@
         <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
@@ -6998,22 +6998,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7076,10 +7076,10 @@
         <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="M52" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="N52" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M54" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="N54" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -8339,16 +8339,16 @@
         <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB56" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8480,16 +8480,16 @@
         <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
         <v>0</v>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8831,22 +8831,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8903,10 +8903,10 @@
         <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
         <v>0</v>
@@ -8972,22 +8972,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9044,10 +9044,10 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="N63" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9326,7 +9326,7 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Y63" t="n">
         <v>1.75</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.6</v>
+        <v>1.32</v>
       </c>
       <c r="M66" t="n">
-        <v>2.61</v>
+        <v>4.3</v>
       </c>
       <c r="N66" t="n">
-        <v>2.84</v>
+        <v>7.8</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9743,16 +9743,16 @@
         <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z66" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
       <c r="M67" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="N67" t="n">
-        <v>7.8</v>
+        <v>2.84</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9884,16 +9884,16 @@
         <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
-        <v>4.01</v>
+        <v>3.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N69" t="n">
-        <v>3.5</v>
+        <v>4.01</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.85</v>
+        <v>1.28</v>
       </c>
       <c r="M71" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="N71" t="n">
-        <v>3.95</v>
+        <v>12</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.28</v>
+        <v>1.85</v>
       </c>
       <c r="M72" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="N72" t="n">
-        <v>12</v>
+        <v>3.95</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -10595,10 +10595,10 @@
         <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO73"/>
+  <dimension ref="A1:AO74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2135,16 +2135,16 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,16 +2558,16 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -3050,22 +3050,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="M19" t="n">
-        <v>2.99</v>
+        <v>3.83</v>
       </c>
       <c r="N19" t="n">
-        <v>2.98</v>
+        <v>3.47</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3101,43 +3101,43 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.88</v>
+        <v>2.16</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3524,25 +3524,25 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X22" t="n">
         <v>2.25</v>
@@ -3551,16 +3551,16 @@
         <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="AO23" s="3" t="n">
-        <v>45894.5625</v>
+        <v>45894.55208333334</v>
       </c>
     </row>
     <row r="24">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.91</v>
+        <v>2.93</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.47</v>
+        <v>1.92</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.93</v>
+        <v>3.91</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4032,27 +4032,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="M26" t="n">
-        <v>3.74</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>3.89</v>
+        <v>4.33</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="AO26" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.5625</v>
       </c>
     </row>
     <row r="27">
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="M27" t="n">
-        <v>3.58</v>
+        <v>3.21</v>
       </c>
       <c r="N27" t="n">
-        <v>3.14</v>
+        <v>2.79</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,16 +4250,16 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.36</v>
+        <v>1.92</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="N28" t="n">
-        <v>2.61</v>
+        <v>3.14</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,16 +4391,16 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.13</v>
+        <v>1.54</v>
       </c>
       <c r="M29" t="n">
-        <v>3.27</v>
+        <v>3.95</v>
       </c>
       <c r="N29" t="n">
-        <v>2.91</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,16 +4532,16 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="M30" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.34</v>
+        <v>1.68</v>
       </c>
       <c r="M32" t="n">
-        <v>3.01</v>
+        <v>3.74</v>
       </c>
       <c r="N32" t="n">
-        <v>2.78</v>
+        <v>3.89</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.94</v>
+        <v>2.34</v>
       </c>
       <c r="M34" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="N34" t="n">
-        <v>3.61</v>
+        <v>2.78</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.54</v>
+        <v>1.94</v>
       </c>
       <c r="M35" t="n">
-        <v>3.95</v>
+        <v>3.06</v>
       </c>
       <c r="N35" t="n">
-        <v>4.6</v>
+        <v>3.61</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,16 +5378,16 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -5447,22 +5447,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.03</v>
+        <v>2.36</v>
       </c>
       <c r="M36" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="N36" t="n">
-        <v>3.1</v>
+        <v>2.61</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5519,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
@@ -5583,12 +5583,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N37" t="n">
-        <v>4.6</v>
+        <v>3.19</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5715,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="AO37" s="3" t="n">
-        <v>45894.60416666666</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="38">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.1</v>
+        <v>1.77</v>
       </c>
       <c r="M41" t="n">
         <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>1.69</v>
+        <v>4.6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6288,12 +6288,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6420,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="AO42" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="43">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6653,10 +6653,10 @@
         <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6998,22 +6998,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7076,10 +7076,10 @@
         <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
@@ -7134,12 +7134,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="AO48" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="49">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7548,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="AO50" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="51">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7980,12 +7980,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8057,10 +8057,10 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="AO54" s="3" t="n">
-        <v>45894.65625</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="55">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -8198,10 +8198,10 @@
         <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -8253,7 +8253,7 @@
         <v>0</v>
       </c>
       <c r="AO55" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.65625</v>
       </c>
     </row>
     <row r="56">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -8339,16 +8339,16 @@
         <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8480,16 +8480,16 @@
         <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB57" t="n">
         <v>0</v>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8826,27 +8826,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8958,7 +8958,7 @@
         <v>0</v>
       </c>
       <c r="AO60" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="61">
@@ -9108,27 +9108,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -9240,7 +9240,7 @@
         <v>0</v>
       </c>
       <c r="AO62" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="63">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9326,10 +9326,10 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9467,10 +9467,10 @@
         <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9608,10 +9608,10 @@
         <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>
@@ -9672,27 +9672,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9749,10 +9749,10 @@
         <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
         <v>0</v>
@@ -9804,7 +9804,7 @@
         <v>0</v>
       </c>
       <c r="AO66" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="67">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.12</v>
+        <v>1.32</v>
       </c>
       <c r="M68" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="N68" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10031,10 +10031,10 @@
         <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -10086,7 +10086,7 @@
         <v>0</v>
       </c>
       <c r="AO68" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="69">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AO70" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="71">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -10509,7 +10509,7 @@
         <v>0</v>
       </c>
       <c r="AO71" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.83333333334</v>
       </c>
     </row>
     <row r="72">
@@ -10659,138 +10659,279 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M73" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N73" t="n">
+        <v>12</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="inlineStr">
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L73" t="n">
+      <c r="L74" t="n">
         <v>1.64</v>
       </c>
-      <c r="M73" t="n">
+      <c r="M74" t="n">
         <v>3.35</v>
       </c>
-      <c r="N73" t="n">
+      <c r="N74" t="n">
         <v>5.2</v>
       </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" t="n">
-        <v>0</v>
-      </c>
-      <c r="W73" t="n">
-        <v>0</v>
-      </c>
-      <c r="X73" t="n">
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" t="n">
         <v>2.1</v>
       </c>
-      <c r="Y73" t="n">
+      <c r="Y74" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO73" s="3" t="n">
+      <c r="Z74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3" t="n">
         <v>45894.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3050,22 +3050,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,16 +3122,16 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.47</v>
+        <v>1.83</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>2.93</v>
+        <v>4.33</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.91</v>
+        <v>2.93</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>4.33</v>
+        <v>3.91</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,16 +4391,16 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.54</v>
+        <v>2.34</v>
       </c>
       <c r="M29" t="n">
-        <v>3.95</v>
+        <v>3.01</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>2.78</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,16 +4532,16 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="N30" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="M31" t="n">
-        <v>3.27</v>
+        <v>3.58</v>
       </c>
       <c r="N31" t="n">
-        <v>2.91</v>
+        <v>3.14</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4814,16 +4814,16 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="M34" t="n">
-        <v>3.01</v>
+        <v>3.27</v>
       </c>
       <c r="N34" t="n">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.36</v>
+        <v>1.54</v>
       </c>
       <c r="M36" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="N36" t="n">
-        <v>2.61</v>
+        <v>4.6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5519,16 +5519,16 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.88</v>
+        <v>1.36</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.88</v>
+        <v>2.9</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
@@ -5588,22 +5588,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="M37" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>3.19</v>
+        <v>2.61</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.1</v>
+        <v>1.77</v>
       </c>
       <c r="M40" t="n">
         <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>1.69</v>
+        <v>4.6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.45</v>
+        <v>4.1</v>
       </c>
       <c r="M42" t="n">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>2.74</v>
+        <v>1.69</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6653,10 +6653,10 @@
         <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -6716,22 +6716,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7634,10 +7634,10 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7775,10 +7775,10 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8480,16 +8480,16 @@
         <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
         <v>0</v>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8585,13 +8585,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8621,16 +8621,16 @@
         <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB58" t="n">
         <v>0</v>
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8972,22 +8972,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9044,10 +9044,10 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -9113,22 +9113,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="M64" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="N64" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9467,10 +9467,10 @@
         <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="M65" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="N65" t="n">
-        <v>3.52</v>
+        <v>3.05</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9608,10 +9608,10 @@
         <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.6</v>
+        <v>1.32</v>
       </c>
       <c r="M67" t="n">
-        <v>2.61</v>
+        <v>4.3</v>
       </c>
       <c r="N67" t="n">
-        <v>2.84</v>
+        <v>7.8</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9884,16 +9884,16 @@
         <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
       <c r="M68" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="N68" t="n">
-        <v>7.8</v>
+        <v>2.84</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10025,16 +10025,16 @@
         <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X68" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="M69" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N69" t="n">
-        <v>4.01</v>
+        <v>3.5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="M70" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N70" t="n">
-        <v>3.5</v>
+        <v>4.01</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO74"/>
+  <dimension ref="A1:AO75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2276,16 +2276,16 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,16 +2558,16 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3101,43 +3101,43 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.83</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3524,43 +3524,43 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3609,27 +3609,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,16 +3686,16 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="AO23" s="3" t="n">
-        <v>45894.55208333334</v>
+        <v>45894.54166666666</v>
       </c>
     </row>
     <row r="24">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="AO24" s="3" t="n">
-        <v>45894.5625</v>
+        <v>45894.55208333334</v>
       </c>
     </row>
     <row r="25">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.47</v>
+        <v>1.92</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.93</v>
+        <v>3.91</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>3.91</v>
+        <v>2.93</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -4173,27 +4173,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.22</v>
+        <v>1.83</v>
       </c>
       <c r="M27" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>2.79</v>
+        <v>4.33</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,10 +4250,10 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="AO27" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.5625</v>
       </c>
     </row>
     <row r="28">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="M29" t="n">
-        <v>3.01</v>
+        <v>3.27</v>
       </c>
       <c r="N29" t="n">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,10 +4532,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="M30" t="n">
-        <v>3.28</v>
+        <v>3.74</v>
       </c>
       <c r="N30" t="n">
-        <v>3.19</v>
+        <v>3.89</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="N31" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4814,16 +4814,16 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.68</v>
+        <v>2.75</v>
       </c>
       <c r="M32" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>3.89</v>
+        <v>2.35</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="M33" t="n">
-        <v>3.29</v>
+        <v>3.58</v>
       </c>
       <c r="N33" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,16 +5096,16 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.79</v>
+        <v>2.4</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.13</v>
+        <v>2.34</v>
       </c>
       <c r="M34" t="n">
-        <v>3.27</v>
+        <v>3.01</v>
       </c>
       <c r="N34" t="n">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5724,27 +5724,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.45</v>
+        <v>2.22</v>
       </c>
       <c r="M38" t="n">
-        <v>3.37</v>
+        <v>3.21</v>
       </c>
       <c r="N38" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -5856,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="AO38" s="3" t="n">
-        <v>45894.60416666666</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6561,7 +6561,7 @@
         <v>0</v>
       </c>
       <c r="AO43" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="44">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7407,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="AO49" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="50">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7634,10 +7634,10 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -7689,7 +7689,7 @@
         <v>0</v>
       </c>
       <c r="AO51" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="52">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8057,10 +8057,10 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -8121,12 +8121,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.43</v>
+        <v>2.19</v>
       </c>
       <c r="M55" t="n">
-        <v>4.5</v>
+        <v>2.98</v>
       </c>
       <c r="N55" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -8198,10 +8198,10 @@
         <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -8253,7 +8253,7 @@
         <v>0</v>
       </c>
       <c r="AO55" s="3" t="n">
-        <v>45894.65625</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="56">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -8339,10 +8339,10 @@
         <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -8394,7 +8394,7 @@
         <v>0</v>
       </c>
       <c r="AO56" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.65625</v>
       </c>
     </row>
     <row r="57">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8867,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8967,27 +8967,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9099,7 +9099,7 @@
         <v>0</v>
       </c>
       <c r="AO61" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="62">
@@ -9113,22 +9113,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
         <v>0</v>
@@ -9249,12 +9249,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9326,10 +9326,10 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -9381,7 +9381,7 @@
         <v>0</v>
       </c>
       <c r="AO63" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="64">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9467,10 +9467,10 @@
         <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9608,10 +9608,10 @@
         <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9749,10 +9749,10 @@
         <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z66" t="n">
         <v>0</v>
@@ -9813,27 +9813,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.32</v>
+        <v>2.35</v>
       </c>
       <c r="M67" t="n">
-        <v>4.3</v>
+        <v>3.16</v>
       </c>
       <c r="N67" t="n">
-        <v>7.8</v>
+        <v>3.05</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9890,10 +9890,10 @@
         <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -9945,7 +9945,7 @@
         <v>0</v>
       </c>
       <c r="AO67" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="68">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.12</v>
+        <v>1.32</v>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="N69" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10172,10 +10172,10 @@
         <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z69" t="n">
         <v>0</v>
@@ -10227,7 +10227,7 @@
         <v>0</v>
       </c>
       <c r="AO69" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="70">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10509,7 +10509,7 @@
         <v>0</v>
       </c>
       <c r="AO71" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="72">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -10595,10 +10595,10 @@
         <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -10650,7 +10650,7 @@
         <v>0</v>
       </c>
       <c r="AO72" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.83333333334</v>
       </c>
     </row>
     <row r="73">
@@ -10800,138 +10800,279 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Delfin SC</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M74" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N74" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" t="inlineStr">
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L74" t="n">
+      <c r="L75" t="n">
         <v>1.64</v>
       </c>
-      <c r="M74" t="n">
+      <c r="M75" t="n">
         <v>3.35</v>
       </c>
-      <c r="N74" t="n">
+      <c r="N75" t="n">
         <v>5.2</v>
       </c>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" t="n">
-        <v>0</v>
-      </c>
-      <c r="V74" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" t="n">
-        <v>0</v>
-      </c>
-      <c r="X74" t="n">
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
         <v>2.1</v>
       </c>
-      <c r="Y74" t="n">
+      <c r="Y75" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO74" s="3" t="n">
+      <c r="Z75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3" t="n">
         <v>45894.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO75"/>
+  <dimension ref="A1:AK69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,130 +513,110 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Odd_D_HT</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Odd_A_HT</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over05</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under05</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>FT_Odd_Over05</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over15</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under15</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over35</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under35</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>homeGoals</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>awayGoals</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_H_HT1</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_HT1</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_HT1</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_DNB_H</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_DNB_A</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -742,18 +722,18 @@
       <c r="AC2" t="n">
         <v>0</v>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD2" t="n">
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF2" t="n">
-        <v>0</v>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -767,19 +747,7 @@
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" s="3" t="n">
+      <c r="AK2" s="3" t="n">
         <v>45894</v>
       </c>
     </row>
@@ -883,18 +851,18 @@
       <c r="AC3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD3" t="n">
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF3" t="n">
-        <v>0</v>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -908,19 +876,7 @@
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="3" t="n">
+      <c r="AK3" s="3" t="n">
         <v>45894.35416666666</v>
       </c>
     </row>
@@ -1013,29 +969,29 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
         <v>1.93</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>1.87</v>
       </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD4" t="n">
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF4" t="n">
-        <v>0</v>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1049,19 +1005,7 @@
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" s="3" t="n">
+      <c r="AK4" s="3" t="n">
         <v>45894.375</v>
       </c>
     </row>
@@ -1086,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1165,18 +1109,18 @@
       <c r="AC5" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD5" t="n">
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF5" t="n">
-        <v>0</v>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1190,19 +1134,7 @@
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" s="3" t="n">
+      <c r="AK5" s="3" t="n">
         <v>45894.4375</v>
       </c>
     </row>
@@ -1227,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1306,18 +1238,18 @@
       <c r="AC6" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD6" t="n">
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF6" t="n">
-        <v>0</v>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1331,19 +1263,7 @@
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" s="3" t="n">
+      <c r="AK6" s="3" t="n">
         <v>45894.4375</v>
       </c>
     </row>
@@ -1368,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1447,18 +1367,18 @@
       <c r="AC7" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD7" t="n">
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF7" t="n">
-        <v>0</v>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1472,19 +1392,7 @@
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="3" t="n">
+      <c r="AK7" s="3" t="n">
         <v>45894.4375</v>
       </c>
     </row>
@@ -1509,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1588,18 +1496,18 @@
       <c r="AC8" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD8" t="n">
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF8" t="n">
-        <v>0</v>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -1613,19 +1521,7 @@
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" s="3" t="n">
+      <c r="AK8" s="3" t="n">
         <v>45894.4375</v>
       </c>
     </row>
@@ -1729,18 +1625,18 @@
       <c r="AC9" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD9" t="n">
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF9" t="n">
-        <v>0</v>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -1754,19 +1650,7 @@
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="3" t="n">
+      <c r="AK9" s="3" t="n">
         <v>45894.4375</v>
       </c>
     </row>
@@ -1853,14 +1737,14 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
         <v>2.25</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
@@ -1870,18 +1754,18 @@
       <c r="AC10" t="n">
         <v>0</v>
       </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD10" t="n">
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF10" t="n">
-        <v>0</v>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -1895,19 +1779,7 @@
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" s="3" t="n">
+      <c r="AK10" s="3" t="n">
         <v>45894.45833333334</v>
       </c>
     </row>
@@ -2011,18 +1883,18 @@
       <c r="AC11" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD11" t="n">
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF11" t="n">
-        <v>0</v>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2036,19 +1908,7 @@
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="3" t="n">
+      <c r="AK11" s="3" t="n">
         <v>45894.47916666666</v>
       </c>
     </row>
@@ -2063,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2152,18 +2012,18 @@
       <c r="AC12" t="n">
         <v>0</v>
       </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD12" t="n">
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF12" t="n">
-        <v>0</v>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2177,19 +2037,7 @@
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="3" t="n">
+      <c r="AK12" s="3" t="n">
         <v>45894.5</v>
       </c>
     </row>
@@ -2204,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2276,16 +2124,16 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2293,18 +2141,18 @@
       <c r="AC13" t="n">
         <v>0</v>
       </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD13" t="n">
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF13" t="n">
-        <v>0</v>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -2318,19 +2166,7 @@
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="3" t="n">
+      <c r="AK13" s="3" t="n">
         <v>45894.5</v>
       </c>
     </row>
@@ -2345,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2434,18 +2270,18 @@
       <c r="AC14" t="n">
         <v>0</v>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD14" t="n">
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF14" t="n">
-        <v>0</v>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -2459,19 +2295,7 @@
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="3" t="n">
+      <c r="AK14" s="3" t="n">
         <v>45894.5</v>
       </c>
     </row>
@@ -2486,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2561,32 +2385,32 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD15" t="n">
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF15" t="n">
-        <v>0</v>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -2600,19 +2424,7 @@
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="3" t="n">
+      <c r="AK15" s="3" t="n">
         <v>45894.5</v>
       </c>
     </row>
@@ -2716,18 +2528,18 @@
       <c r="AC16" t="n">
         <v>0</v>
       </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD16" t="n">
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF16" t="n">
-        <v>0</v>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -2741,19 +2553,7 @@
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" s="3" t="n">
+      <c r="AK16" s="3" t="n">
         <v>45894.52083333334</v>
       </c>
     </row>
@@ -2857,18 +2657,18 @@
       <c r="AC17" t="n">
         <v>0</v>
       </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD17" t="n">
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF17" t="n">
-        <v>0</v>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -2882,19 +2682,7 @@
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" s="3" t="n">
+      <c r="AK17" s="3" t="n">
         <v>45894.53125</v>
       </c>
     </row>
@@ -2998,18 +2786,18 @@
       <c r="AC18" t="n">
         <v>0</v>
       </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD18" t="n">
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF18" t="n">
-        <v>0</v>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -3023,19 +2811,7 @@
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" s="3" t="n">
+      <c r="AK18" s="3" t="n">
         <v>45894.53125</v>
       </c>
     </row>
@@ -3050,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="M19" t="n">
-        <v>2.99</v>
+        <v>3.83</v>
       </c>
       <c r="N19" t="n">
-        <v>2.98</v>
+        <v>3.47</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3101,82 +2877,70 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.88</v>
+        <v>2.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.22</v>
+        <v>2.16</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF19" t="n">
-        <v>1.33</v>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="3" t="n">
         <v>45894.54166666666</v>
       </c>
     </row>
@@ -3280,18 +3044,18 @@
       <c r="AC20" t="n">
         <v>0</v>
       </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD20" t="n">
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF20" t="n">
-        <v>0</v>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -3305,19 +3069,7 @@
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" s="3" t="n">
+      <c r="AK20" s="3" t="n">
         <v>45894.54166666666</v>
       </c>
     </row>
@@ -3332,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,10 +3156,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3421,18 +3173,18 @@
       <c r="AC21" t="n">
         <v>0</v>
       </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD21" t="n">
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF21" t="n">
-        <v>0</v>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -3446,19 +3198,7 @@
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" s="3" t="n">
+      <c r="AK21" s="3" t="n">
         <v>45894.54166666666</v>
       </c>
     </row>
@@ -3468,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3562,18 +3302,18 @@
       <c r="AC22" t="n">
         <v>0</v>
       </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD22" t="n">
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF22" t="n">
-        <v>0</v>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -3587,20 +3327,8 @@
       <c r="AJ22" t="n">
         <v>0</v>
       </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" s="3" t="n">
-        <v>45894.54166666666</v>
+      <c r="AK22" s="3" t="n">
+        <v>45894.55208333334</v>
       </c>
     </row>
     <row r="23">
@@ -3609,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="M23" t="n">
-        <v>3.83</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3.47</v>
+        <v>4.33</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3686,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.16</v>
+        <v>1.65</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3703,18 +3431,18 @@
       <c r="AC23" t="n">
         <v>0</v>
       </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD23" t="n">
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF23" t="n">
-        <v>0</v>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -3728,20 +3456,8 @@
       <c r="AJ23" t="n">
         <v>0</v>
       </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" s="3" t="n">
-        <v>45894.54166666666</v>
+      <c r="AK23" s="3" t="n">
+        <v>45894.5625</v>
       </c>
     </row>
     <row r="24">
@@ -3750,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3830,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3844,18 +3560,18 @@
       <c r="AC24" t="n">
         <v>0</v>
       </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD24" t="n">
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF24" t="n">
-        <v>0</v>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -3869,20 +3585,8 @@
       <c r="AJ24" t="n">
         <v>0</v>
       </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO24" s="3" t="n">
-        <v>45894.55208333334</v>
+      <c r="AK24" s="3" t="n">
+        <v>45894.5625</v>
       </c>
     </row>
     <row r="25">
@@ -3896,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.91</v>
+        <v>2.93</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3672,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -3985,18 +3689,18 @@
       <c r="AC25" t="n">
         <v>0</v>
       </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD25" t="n">
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF25" t="n">
-        <v>0</v>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -4010,19 +3714,7 @@
       <c r="AJ25" t="n">
         <v>0</v>
       </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" s="3" t="n">
+      <c r="AK25" s="3" t="n">
         <v>45894.5625</v>
       </c>
     </row>
@@ -4032,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="N26" t="n">
-        <v>2.93</v>
+        <v>3.19</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4126,18 +3818,18 @@
       <c r="AC26" t="n">
         <v>0</v>
       </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD26" t="n">
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF26" t="n">
-        <v>0</v>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -4151,20 +3843,8 @@
       <c r="AJ26" t="n">
         <v>0</v>
       </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" s="3" t="n">
-        <v>45894.5625</v>
+      <c r="AK26" s="3" t="n">
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="27">
@@ -4173,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="N27" t="n">
-        <v>4.33</v>
+        <v>2.91</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,13 +3930,13 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4267,18 +3947,18 @@
       <c r="AC27" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD27" t="n">
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF27" t="n">
-        <v>0</v>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -4292,20 +3972,8 @@
       <c r="AJ27" t="n">
         <v>0</v>
       </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" s="3" t="n">
-        <v>45894.5625</v>
+      <c r="AK27" s="3" t="n">
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="28">
@@ -4319,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.03</v>
+        <v>1.54</v>
       </c>
       <c r="M28" t="n">
-        <v>3.29</v>
+        <v>3.95</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,35 +4059,35 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
       </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD28" t="n">
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF28" t="n">
-        <v>0</v>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -4433,19 +4101,7 @@
       <c r="AJ28" t="n">
         <v>0</v>
       </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" s="3" t="n">
+      <c r="AK28" s="3" t="n">
         <v>45894.58333333334</v>
       </c>
     </row>
@@ -4460,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="M29" t="n">
-        <v>3.27</v>
+        <v>3.58</v>
       </c>
       <c r="N29" t="n">
-        <v>2.91</v>
+        <v>3.14</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,35 +4188,35 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
       </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD29" t="n">
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF29" t="n">
-        <v>0</v>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -4574,19 +4230,7 @@
       <c r="AJ29" t="n">
         <v>0</v>
       </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" s="3" t="n">
+      <c r="AK29" s="3" t="n">
         <v>45894.58333333334</v>
       </c>
     </row>
@@ -4690,18 +4334,18 @@
       <c r="AC30" t="n">
         <v>0</v>
       </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD30" t="n">
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF30" t="n">
-        <v>0</v>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -4715,19 +4359,7 @@
       <c r="AJ30" t="n">
         <v>0</v>
       </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" s="3" t="n">
+      <c r="AK30" s="3" t="n">
         <v>45894.58333333334</v>
       </c>
     </row>
@@ -4742,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="M31" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="N31" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4817,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4831,18 +4463,18 @@
       <c r="AC31" t="n">
         <v>0</v>
       </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD31" t="n">
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF31" t="n">
-        <v>0</v>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -4856,19 +4488,7 @@
       <c r="AJ31" t="n">
         <v>0</v>
       </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" s="3" t="n">
+      <c r="AK31" s="3" t="n">
         <v>45894.58333333334</v>
       </c>
     </row>
@@ -4883,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.75</v>
+        <v>1.94</v>
       </c>
       <c r="M32" t="n">
-        <v>3.45</v>
+        <v>3.06</v>
       </c>
       <c r="N32" t="n">
-        <v>2.35</v>
+        <v>3.61</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,10 +4575,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -4972,18 +4592,18 @@
       <c r="AC32" t="n">
         <v>0</v>
       </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD32" t="n">
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF32" t="n">
-        <v>0</v>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -4997,19 +4617,7 @@
       <c r="AJ32" t="n">
         <v>0</v>
       </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" s="3" t="n">
+      <c r="AK32" s="3" t="n">
         <v>45894.58333333334</v>
       </c>
     </row>
@@ -5024,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.92</v>
+        <v>2.75</v>
       </c>
       <c r="M33" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>3.14</v>
+        <v>2.35</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,16 +4704,16 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5113,18 +4721,18 @@
       <c r="AC33" t="n">
         <v>0</v>
       </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD33" t="n">
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF33" t="n">
-        <v>0</v>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -5138,19 +4746,7 @@
       <c r="AJ33" t="n">
         <v>0</v>
       </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" s="3" t="n">
+      <c r="AK33" s="3" t="n">
         <v>45894.58333333334</v>
       </c>
     </row>
@@ -5254,18 +4850,18 @@
       <c r="AC34" t="n">
         <v>0</v>
       </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD34" t="n">
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF34" t="n">
-        <v>0</v>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -5279,19 +4875,7 @@
       <c r="AJ34" t="n">
         <v>0</v>
       </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" s="3" t="n">
+      <c r="AK34" s="3" t="n">
         <v>45894.58333333334</v>
       </c>
     </row>
@@ -5316,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.94</v>
+        <v>2.36</v>
       </c>
       <c r="M35" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="N35" t="n">
-        <v>3.61</v>
+        <v>2.61</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5381,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5395,18 +4979,18 @@
       <c r="AC35" t="n">
         <v>0</v>
       </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD35" t="n">
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF35" t="n">
-        <v>0</v>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -5420,19 +5004,7 @@
       <c r="AJ35" t="n">
         <v>0</v>
       </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO35" s="3" t="n">
+      <c r="AK35" s="3" t="n">
         <v>45894.58333333334</v>
       </c>
     </row>
@@ -5447,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.54</v>
+        <v>2.22</v>
       </c>
       <c r="M36" t="n">
-        <v>3.95</v>
+        <v>3.21</v>
       </c>
       <c r="N36" t="n">
-        <v>4.6</v>
+        <v>2.79</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5519,16 +5091,16 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.9</v>
+        <v>1.75</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
@@ -5536,18 +5108,18 @@
       <c r="AC36" t="n">
         <v>0</v>
       </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD36" t="n">
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF36" t="n">
-        <v>0</v>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -5561,19 +5133,7 @@
       <c r="AJ36" t="n">
         <v>0</v>
       </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO36" s="3" t="n">
+      <c r="AK36" s="3" t="n">
         <v>45894.58333333334</v>
       </c>
     </row>
@@ -5583,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5220,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5677,18 +5237,18 @@
       <c r="AC37" t="n">
         <v>0</v>
       </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD37" t="n">
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF37" t="n">
-        <v>0</v>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -5702,20 +5262,8 @@
       <c r="AJ37" t="n">
         <v>0</v>
       </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO37" s="3" t="n">
-        <v>45894.58333333334</v>
+      <c r="AK37" s="3" t="n">
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="38">
@@ -5724,27 +5272,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="M38" t="n">
-        <v>3.21</v>
+        <v>3.37</v>
       </c>
       <c r="N38" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,13 +5349,13 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5818,18 +5366,18 @@
       <c r="AC38" t="n">
         <v>0</v>
       </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD38" t="n">
+        <v>0</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF38" t="n">
-        <v>0</v>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -5843,20 +5391,8 @@
       <c r="AJ38" t="n">
         <v>0</v>
       </c>
-      <c r="AK38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO38" s="3" t="n">
-        <v>45894.58333333334</v>
+      <c r="AK38" s="3" t="n">
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="39">
@@ -5870,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.77</v>
+        <v>4.1</v>
       </c>
       <c r="M39" t="n">
         <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>4.6</v>
+        <v>1.69</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,13 +5478,13 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5959,18 +5495,18 @@
       <c r="AC39" t="n">
         <v>0</v>
       </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD39" t="n">
+        <v>0</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF39" t="n">
-        <v>0</v>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -5984,19 +5520,7 @@
       <c r="AJ39" t="n">
         <v>0</v>
       </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" s="3" t="n">
+      <c r="AK39" s="3" t="n">
         <v>45894.60416666666</v>
       </c>
     </row>
@@ -6006,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6100,18 +5624,18 @@
       <c r="AC40" t="n">
         <v>0</v>
       </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD40" t="n">
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF40" t="n">
-        <v>0</v>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -6125,20 +5649,8 @@
       <c r="AJ40" t="n">
         <v>0</v>
       </c>
-      <c r="AK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" s="3" t="n">
-        <v>45894.60416666666</v>
+      <c r="AK40" s="3" t="n">
+        <v>45894.625</v>
       </c>
     </row>
     <row r="41">
@@ -6147,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6241,18 +5753,18 @@
       <c r="AC41" t="n">
         <v>0</v>
       </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD41" t="n">
+        <v>0</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF41" t="n">
-        <v>0</v>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -6266,20 +5778,8 @@
       <c r="AJ41" t="n">
         <v>0</v>
       </c>
-      <c r="AK41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO41" s="3" t="n">
-        <v>45894.60416666666</v>
+      <c r="AK41" s="3" t="n">
+        <v>45894.625</v>
       </c>
     </row>
     <row r="42">
@@ -6288,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +5865,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6382,18 +5882,18 @@
       <c r="AC42" t="n">
         <v>0</v>
       </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD42" t="n">
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF42" t="n">
-        <v>0</v>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -6407,20 +5907,8 @@
       <c r="AJ42" t="n">
         <v>0</v>
       </c>
-      <c r="AK42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO42" s="3" t="n">
-        <v>45894.60416666666</v>
+      <c r="AK42" s="3" t="n">
+        <v>45894.625</v>
       </c>
     </row>
     <row r="43">
@@ -6429,27 +5917,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="M43" t="n">
-        <v>3.37</v>
+        <v>4.6</v>
       </c>
       <c r="N43" t="n">
-        <v>2.74</v>
+        <v>4.05</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,35 +5994,35 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
       </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD43" t="n">
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF43" t="n">
-        <v>0</v>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -6548,20 +6036,8 @@
       <c r="AJ43" t="n">
         <v>0</v>
       </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO43" s="3" t="n">
-        <v>45894.60416666666</v>
+      <c r="AK43" s="3" t="n">
+        <v>45894.625</v>
       </c>
     </row>
     <row r="44">
@@ -6585,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6664,18 +6140,18 @@
       <c r="AC44" t="n">
         <v>0</v>
       </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD44" t="n">
+        <v>0</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF44" t="n">
-        <v>0</v>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -6689,19 +6165,7 @@
       <c r="AJ44" t="n">
         <v>0</v>
       </c>
-      <c r="AK44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO44" s="3" t="n">
+      <c r="AK44" s="3" t="n">
         <v>45894.625</v>
       </c>
     </row>
@@ -6716,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6794,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
@@ -6805,18 +6269,18 @@
       <c r="AC45" t="n">
         <v>0</v>
       </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD45" t="n">
+        <v>0</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF45" t="n">
-        <v>0</v>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -6830,19 +6294,7 @@
       <c r="AJ45" t="n">
         <v>0</v>
       </c>
-      <c r="AK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO45" s="3" t="n">
+      <c r="AK45" s="3" t="n">
         <v>45894.625</v>
       </c>
     </row>
@@ -6852,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6946,18 +6398,18 @@
       <c r="AC46" t="n">
         <v>0</v>
       </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD46" t="n">
+        <v>0</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF46" t="n">
-        <v>0</v>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -6971,20 +6423,8 @@
       <c r="AJ46" t="n">
         <v>0</v>
       </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO46" s="3" t="n">
-        <v>45894.625</v>
+      <c r="AK46" s="3" t="n">
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="47">
@@ -6993,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7087,18 +6527,18 @@
       <c r="AC47" t="n">
         <v>0</v>
       </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD47" t="n">
+        <v>0</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF47" t="n">
-        <v>0</v>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -7112,20 +6552,8 @@
       <c r="AJ47" t="n">
         <v>0</v>
       </c>
-      <c r="AK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO47" s="3" t="n">
-        <v>45894.625</v>
+      <c r="AK47" s="3" t="n">
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="48">
@@ -7134,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7228,18 +6656,18 @@
       <c r="AC48" t="n">
         <v>0</v>
       </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD48" t="n">
+        <v>0</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF48" t="n">
-        <v>0</v>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -7253,20 +6681,8 @@
       <c r="AJ48" t="n">
         <v>0</v>
       </c>
-      <c r="AK48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO48" s="3" t="n">
-        <v>45894.625</v>
+      <c r="AK48" s="3" t="n">
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="49">
@@ -7275,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7355,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -7369,18 +6785,18 @@
       <c r="AC49" t="n">
         <v>0</v>
       </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD49" t="n">
+        <v>0</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF49" t="n">
-        <v>0</v>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -7394,20 +6810,8 @@
       <c r="AJ49" t="n">
         <v>0</v>
       </c>
-      <c r="AK49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO49" s="3" t="n">
-        <v>45894.625</v>
+      <c r="AK49" s="3" t="n">
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="50">
@@ -7416,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7510,18 +6914,18 @@
       <c r="AC50" t="n">
         <v>0</v>
       </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD50" t="n">
+        <v>0</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF50" t="n">
-        <v>0</v>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -7535,20 +6939,8 @@
       <c r="AJ50" t="n">
         <v>0</v>
       </c>
-      <c r="AK50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO50" s="3" t="n">
-        <v>45894.63541666666</v>
+      <c r="AK50" s="3" t="n">
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="51">
@@ -7557,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7637,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7651,18 +7043,18 @@
       <c r="AC51" t="n">
         <v>0</v>
       </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD51" t="n">
+        <v>0</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF51" t="n">
-        <v>0</v>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -7676,20 +7068,8 @@
       <c r="AJ51" t="n">
         <v>0</v>
       </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO51" s="3" t="n">
-        <v>45894.63541666666</v>
+      <c r="AK51" s="3" t="n">
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="52">
@@ -7698,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7778,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7792,18 +7172,18 @@
       <c r="AC52" t="n">
         <v>0</v>
       </c>
-      <c r="AD52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD52" t="n">
+        <v>0</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF52" t="n">
-        <v>0</v>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -7817,20 +7197,8 @@
       <c r="AJ52" t="n">
         <v>0</v>
       </c>
-      <c r="AK52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO52" s="3" t="n">
-        <v>45894.64583333334</v>
+      <c r="AK52" s="3" t="n">
+        <v>45894.65625</v>
       </c>
     </row>
     <row r="53">
@@ -7839,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7919,32 +7287,32 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
       </c>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD53" t="n">
+        <v>0</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF53" t="n">
-        <v>0</v>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -7958,20 +7326,8 @@
       <c r="AJ53" t="n">
         <v>0</v>
       </c>
-      <c r="AK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO53" s="3" t="n">
-        <v>45894.64583333334</v>
+      <c r="AK53" s="3" t="n">
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="54">
@@ -7980,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.22</v>
+        <v>1.23</v>
       </c>
       <c r="M54" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="N54" t="n">
-        <v>2.86</v>
+        <v>13.2</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8057,10 +7413,10 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -8074,18 +7430,18 @@
       <c r="AC54" t="n">
         <v>0</v>
       </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD54" t="n">
+        <v>0</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF54" t="n">
-        <v>0</v>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -8099,20 +7455,8 @@
       <c r="AJ54" t="n">
         <v>0</v>
       </c>
-      <c r="AK54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO54" s="3" t="n">
-        <v>45894.64583333334</v>
+      <c r="AK54" s="3" t="n">
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="55">
@@ -8121,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8162,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
       <c r="M55" t="n">
-        <v>2.98</v>
+        <v>3.16</v>
       </c>
       <c r="N55" t="n">
-        <v>3.6</v>
+        <v>3.86</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -8198,10 +7542,10 @@
         <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -8215,18 +7559,18 @@
       <c r="AC55" t="n">
         <v>0</v>
       </c>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD55" t="n">
+        <v>0</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF55" t="n">
-        <v>0</v>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -8240,20 +7584,8 @@
       <c r="AJ55" t="n">
         <v>0</v>
       </c>
-      <c r="AK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO55" s="3" t="n">
-        <v>45894.64583333334</v>
+      <c r="AK55" s="3" t="n">
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="56">
@@ -8262,12 +7594,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8303,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="M56" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="N56" t="n">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -8339,10 +7671,10 @@
         <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -8356,18 +7688,18 @@
       <c r="AC56" t="n">
         <v>0</v>
       </c>
-      <c r="AD56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD56" t="n">
+        <v>0</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF56" t="n">
-        <v>0</v>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -8381,20 +7713,8 @@
       <c r="AJ56" t="n">
         <v>0</v>
       </c>
-      <c r="AK56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO56" s="3" t="n">
-        <v>45894.65625</v>
+      <c r="AK56" s="3" t="n">
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="57">
@@ -8418,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8444,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="M57" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>3.86</v>
+        <v>2.91</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -8497,18 +7817,18 @@
       <c r="AC57" t="n">
         <v>0</v>
       </c>
-      <c r="AD57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD57" t="n">
+        <v>0</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF57" t="n">
-        <v>0</v>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -8522,19 +7842,7 @@
       <c r="AJ57" t="n">
         <v>0</v>
       </c>
-      <c r="AK57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO57" s="3" t="n">
+      <c r="AK57" s="3" t="n">
         <v>45894.66666666666</v>
       </c>
     </row>
@@ -8544,27 +7852,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8585,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8621,16 +7929,16 @@
         <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
         <v>0</v>
@@ -8638,18 +7946,18 @@
       <c r="AC58" t="n">
         <v>0</v>
       </c>
-      <c r="AD58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD58" t="n">
+        <v>0</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF58" t="n">
-        <v>0</v>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -8663,20 +7971,8 @@
       <c r="AJ58" t="n">
         <v>0</v>
       </c>
-      <c r="AK58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO58" s="3" t="n">
-        <v>45894.66666666666</v>
+      <c r="AK58" s="3" t="n">
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="59">
@@ -8685,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8726,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="M59" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N59" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8765,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8779,18 +8075,18 @@
       <c r="AC59" t="n">
         <v>0</v>
       </c>
-      <c r="AD59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD59" t="n">
+        <v>0</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF59" t="n">
-        <v>0</v>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -8804,20 +8100,8 @@
       <c r="AJ59" t="n">
         <v>0</v>
       </c>
-      <c r="AK59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO59" s="3" t="n">
-        <v>45894.66666666666</v>
+      <c r="AK59" s="3" t="n">
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="60">
@@ -8826,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8867,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8920,18 +8204,18 @@
       <c r="AC60" t="n">
         <v>0</v>
       </c>
-      <c r="AD60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD60" t="n">
+        <v>0</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF60" t="n">
-        <v>0</v>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -8945,20 +8229,8 @@
       <c r="AJ60" t="n">
         <v>0</v>
       </c>
-      <c r="AK60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO60" s="3" t="n">
-        <v>45894.66666666666</v>
+      <c r="AK60" s="3" t="n">
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="61">
@@ -8967,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8982,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="M61" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="N61" t="n">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9047,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -9061,18 +8333,18 @@
       <c r="AC61" t="n">
         <v>0</v>
       </c>
-      <c r="AD61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD61" t="n">
+        <v>0</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF61" t="n">
-        <v>0</v>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -9086,20 +8358,8 @@
       <c r="AJ61" t="n">
         <v>0</v>
       </c>
-      <c r="AK61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO61" s="3" t="n">
-        <v>45894.66666666666</v>
+      <c r="AK61" s="3" t="n">
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="62">
@@ -9108,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9182,10 +8442,10 @@
         <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y62" t="n">
         <v>0</v>
@@ -9202,18 +8462,18 @@
       <c r="AC62" t="n">
         <v>0</v>
       </c>
-      <c r="AD62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD62" t="n">
+        <v>0</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF62" t="n">
-        <v>0</v>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -9227,20 +8487,8 @@
       <c r="AJ62" t="n">
         <v>0</v>
       </c>
-      <c r="AK62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO62" s="3" t="n">
-        <v>45894.67708333334</v>
+      <c r="AK62" s="3" t="n">
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="63">
@@ -9249,27 +8497,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.07</v>
+        <v>1.32</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N63" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9326,13 +8574,13 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -9343,18 +8591,18 @@
       <c r="AC63" t="n">
         <v>0</v>
       </c>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD63" t="n">
+        <v>0</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF63" t="n">
-        <v>0</v>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -9368,20 +8616,8 @@
       <c r="AJ63" t="n">
         <v>0</v>
       </c>
-      <c r="AK63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO63" s="3" t="n">
-        <v>45894.67708333334</v>
+      <c r="AK63" s="3" t="n">
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="64">
@@ -9390,27 +8626,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9484,18 +8720,18 @@
       <c r="AC64" t="n">
         <v>0</v>
       </c>
-      <c r="AD64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD64" t="n">
+        <v>0</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF64" t="n">
-        <v>0</v>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -9509,20 +8745,8 @@
       <c r="AJ64" t="n">
         <v>0</v>
       </c>
-      <c r="AK64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO64" s="3" t="n">
-        <v>45894.6875</v>
+      <c r="AK64" s="3" t="n">
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="65">
@@ -9531,27 +8755,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9572,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9625,18 +8849,18 @@
       <c r="AC65" t="n">
         <v>0</v>
       </c>
-      <c r="AD65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD65" t="n">
+        <v>0</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF65" t="n">
-        <v>0</v>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -9650,20 +8874,8 @@
       <c r="AJ65" t="n">
         <v>0</v>
       </c>
-      <c r="AK65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO65" s="3" t="n">
-        <v>45894.6875</v>
+      <c r="AK65" s="3" t="n">
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="66">
@@ -9672,27 +8884,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9749,10 +8961,10 @@
         <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
         <v>0</v>
@@ -9766,18 +8978,18 @@
       <c r="AC66" t="n">
         <v>0</v>
       </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD66" t="n">
+        <v>0</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF66" t="n">
-        <v>0</v>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -9791,20 +9003,8 @@
       <c r="AJ66" t="n">
         <v>0</v>
       </c>
-      <c r="AK66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO66" s="3" t="n">
-        <v>45894.6875</v>
+      <c r="AK66" s="3" t="n">
+        <v>45894.83333333334</v>
       </c>
     </row>
     <row r="67">
@@ -9813,27 +9013,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.35</v>
+        <v>1.28</v>
       </c>
       <c r="M67" t="n">
-        <v>3.16</v>
+        <v>5.3</v>
       </c>
       <c r="N67" t="n">
-        <v>3.05</v>
+        <v>12</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9890,13 +9090,13 @@
         <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9907,18 +9107,18 @@
       <c r="AC67" t="n">
         <v>0</v>
       </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD67" t="n">
+        <v>0</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF67" t="n">
-        <v>0</v>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -9932,20 +9132,8 @@
       <c r="AJ67" t="n">
         <v>0</v>
       </c>
-      <c r="AK67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO67" s="3" t="n">
-        <v>45894.6875</v>
+      <c r="AK67" s="3" t="n">
+        <v>45894.875</v>
       </c>
     </row>
     <row r="68">
@@ -9954,12 +9142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9995,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="M68" t="n">
-        <v>2.61</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>2.84</v>
+        <v>3.95</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -10025,19 +9213,19 @@
         <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -10048,18 +9236,18 @@
       <c r="AC68" t="n">
         <v>0</v>
       </c>
-      <c r="AD68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD68" t="n">
+        <v>0</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF68" t="n">
-        <v>0</v>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -10073,20 +9261,8 @@
       <c r="AJ68" t="n">
         <v>0</v>
       </c>
-      <c r="AK68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO68" s="3" t="n">
-        <v>45894.79166666666</v>
+      <c r="AK68" s="3" t="n">
+        <v>45894.875</v>
       </c>
     </row>
     <row r="69">
@@ -10095,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="M69" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="N69" t="n">
-        <v>7.8</v>
+        <v>5.2</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10172,13 +9348,13 @@
         <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -10189,18 +9365,18 @@
       <c r="AC69" t="n">
         <v>0</v>
       </c>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD69" t="n">
+        <v>0</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF69" t="n">
-        <v>0</v>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -10214,865 +9390,7 @@
       <c r="AJ69" t="n">
         <v>0</v>
       </c>
-      <c r="AK69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO69" s="3" t="n">
-        <v>45894.79166666666</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
-        <v>45894</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Brazil Serie C</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Guarani</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Confiança</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="M70" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N70" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO70" s="3" t="n">
-        <v>45894.8125</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
-        <v>45894</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Brazil Serie C</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>CSA</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Ponte Preta</t>
-        </is>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L71" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="M71" t="n">
-        <v>3</v>
-      </c>
-      <c r="N71" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0</v>
-      </c>
-      <c r="X71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO71" s="3" t="n">
-        <v>45894.8125</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
-        <v>45894</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Real Tomayapo</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" t="n">
-        <v>0</v>
-      </c>
-      <c r="X72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO72" s="3" t="n">
-        <v>45894.83333333334</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
-        <v>45894</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Vitória</t>
-        </is>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L73" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M73" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N73" t="n">
-        <v>12</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" t="n">
-        <v>0</v>
-      </c>
-      <c r="W73" t="n">
-        <v>0</v>
-      </c>
-      <c r="X73" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO73" s="3" t="n">
-        <v>45894.875</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
-        <v>45894</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Orense SC</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Delfin SC</t>
-        </is>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L74" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="M74" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N74" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" t="n">
-        <v>0</v>
-      </c>
-      <c r="V74" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" t="n">
-        <v>0</v>
-      </c>
-      <c r="X74" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO74" s="3" t="n">
-        <v>45894.875</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
-        <v>45894</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L75" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="M75" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N75" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" t="n">
-        <v>0</v>
-      </c>
-      <c r="V75" t="n">
-        <v>0</v>
-      </c>
-      <c r="W75" t="n">
-        <v>0</v>
-      </c>
-      <c r="X75" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO75" s="3" t="n">
+      <c r="AK69" s="3" t="n">
         <v>45894.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK69"/>
+  <dimension ref="A1:AK72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,16 +2256,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,16 +2385,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,43 +2475,43 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.53</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45894.52083333334</v>
+        <v>45894.5</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45894.53125</v>
+        <v>45894.52083333334</v>
       </c>
     </row>
     <row r="18">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,16 +2901,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45894.54166666666</v>
+        <v>45894.53125</v>
       </c>
     </row>
     <row r="20">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45894.55208333334</v>
+        <v>45894.54166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45894.5625</v>
+        <v>45894.55208333334</v>
       </c>
     </row>
     <row r="24">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.91</v>
+        <v>4.33</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.47</v>
+        <v>1.92</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.93</v>
+        <v>3.91</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>2.47</v>
       </c>
       <c r="M26" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>3.19</v>
+        <v>2.93</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.5625</v>
       </c>
     </row>
     <row r="27">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.13</v>
+        <v>2.34</v>
       </c>
       <c r="M27" t="n">
-        <v>3.27</v>
+        <v>3.01</v>
       </c>
       <c r="N27" t="n">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="M28" t="n">
-        <v>3.95</v>
+        <v>3.58</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>3.14</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="N29" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.68</v>
+        <v>2.75</v>
       </c>
       <c r="M30" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>3.89</v>
+        <v>2.35</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="M31" t="n">
-        <v>3.29</v>
+        <v>3.06</v>
       </c>
       <c r="N31" t="n">
-        <v>3.1</v>
+        <v>3.61</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.94</v>
+        <v>1.54</v>
       </c>
       <c r="M32" t="n">
-        <v>3.06</v>
+        <v>3.95</v>
       </c>
       <c r="N32" t="n">
-        <v>3.61</v>
+        <v>4.6</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.35</v>
+        <v>2.61</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="M34" t="n">
-        <v>3.01</v>
+        <v>3.27</v>
       </c>
       <c r="N34" t="n">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="N35" t="n">
-        <v>2.61</v>
+        <v>3.89</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.22</v>
+        <v>2.03</v>
       </c>
       <c r="M36" t="n">
-        <v>3.21</v>
+        <v>3.29</v>
       </c>
       <c r="N36" t="n">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45894.60416666666</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="38">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.45</v>
+        <v>1.77</v>
       </c>
       <c r="M38" t="n">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>2.74</v>
+        <v>4.6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="41">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6003,10 +6003,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6132,10 +6132,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="47">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45894.63541666666</v>
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="50">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="M51" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="N51" t="n">
-        <v>3.6</v>
+        <v>2.86</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45894.65625</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="53">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,16 +7287,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="54">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="M54" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="N54" t="n">
-        <v>13.2</v>
+        <v>6.8</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.65625</v>
       </c>
     </row>
     <row r="55">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="M55" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="N55" t="n">
-        <v>3.86</v>
+        <v>3.2</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="M56" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="N56" t="n">
-        <v>3.2</v>
+        <v>1.92</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,16 +7674,16 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7852,27 +7852,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="59">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="M59" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="N59" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="60">
@@ -8110,27 +8110,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="61">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="M61" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="N61" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="62">
@@ -8368,27 +8368,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="M62" t="n">
-        <v>2.61</v>
+        <v>3.16</v>
       </c>
       <c r="N62" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8442,16 +8442,16 @@
         <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="63">
@@ -8497,27 +8497,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="64">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.12</v>
+        <v>1.32</v>
       </c>
       <c r="M64" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="N64" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="65">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="M65" t="n">
-        <v>3.25</v>
+        <v>2.61</v>
       </c>
       <c r="N65" t="n">
-        <v>4.01</v>
+        <v>2.84</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8829,10 +8829,10 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y65" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="66">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="67">
@@ -9013,12 +9013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.28</v>
+        <v>2.1</v>
       </c>
       <c r="M67" t="n">
-        <v>5.3</v>
+        <v>2.87</v>
       </c>
       <c r="N67" t="n">
-        <v>12</v>
+        <v>3.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9087,16 +9087,16 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="68">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.83333333334</v>
       </c>
     </row>
     <row r="69">
@@ -9271,126 +9271,513 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Deportes Temuco</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M69" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N69" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3" t="n">
+        <v>45894.83333333334</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Delfin SC</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M70" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M71" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N71" t="n">
+        <v>12</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="inlineStr">
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L69" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="M69" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N69" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" t="n">
-        <v>0</v>
-      </c>
-      <c r="W69" t="n">
-        <v>0</v>
-      </c>
-      <c r="X69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z69" t="n">
+      <c r="L72" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK69" s="3" t="n">
+      <c r="M72" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N72" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK72" s="3" t="n">
         <v>45894.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,16 +2256,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="M20" t="n">
-        <v>2.99</v>
+        <v>3.83</v>
       </c>
       <c r="N20" t="n">
-        <v>2.98</v>
+        <v>3.47</v>
       </c>
       <c r="O20" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.88</v>
+        <v>2.16</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.83</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.83</v>
+        <v>2.47</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>4.33</v>
+        <v>2.93</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>3.91</v>
+        <v>4.33</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.47</v>
+        <v>1.92</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.93</v>
+        <v>3.91</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.34</v>
+        <v>1.92</v>
       </c>
       <c r="M27" t="n">
-        <v>3.01</v>
+        <v>3.58</v>
       </c>
       <c r="N27" t="n">
-        <v>2.78</v>
+        <v>3.14</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="N28" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="M29" t="n">
-        <v>3.28</v>
+        <v>3.95</v>
       </c>
       <c r="N29" t="n">
-        <v>3.19</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.75</v>
+        <v>2.03</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.54</v>
+        <v>4.1</v>
       </c>
       <c r="M32" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>4.6</v>
+        <v>1.69</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.9</v>
+        <v>1.89</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="N33" t="n">
-        <v>2.61</v>
+        <v>2.79</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.13</v>
+        <v>1.68</v>
       </c>
       <c r="M34" t="n">
-        <v>3.27</v>
+        <v>3.74</v>
       </c>
       <c r="N34" t="n">
-        <v>2.91</v>
+        <v>3.89</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.68</v>
+        <v>2.75</v>
       </c>
       <c r="M35" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>3.89</v>
+        <v>2.35</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.03</v>
+        <v>2.36</v>
       </c>
       <c r="M36" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="N36" t="n">
-        <v>3.1</v>
+        <v>2.61</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="M37" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="N37" t="n">
-        <v>2.79</v>
+        <v>2.91</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5272,27 +5272,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.77</v>
+        <v>2.34</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="N38" t="n">
-        <v>4.6</v>
+        <v>2.78</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45894.60416666666</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45894.63541666666</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,16 +6670,16 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45894.63541666666</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.6</v>
+        <v>2.26</v>
       </c>
       <c r="M56" t="n">
-        <v>3.95</v>
+        <v>3.18</v>
       </c>
       <c r="N56" t="n">
-        <v>1.92</v>
+        <v>2.93</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,16 +7674,16 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="N57" t="n">
-        <v>2.91</v>
+        <v>3.86</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.91</v>
+        <v>3.6</v>
       </c>
       <c r="M59" t="n">
-        <v>3.16</v>
+        <v>3.95</v>
       </c>
       <c r="N59" t="n">
-        <v>3.86</v>
+        <v>1.92</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,16 +8061,16 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
       <c r="M64" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="N64" t="n">
-        <v>7.8</v>
+        <v>2.84</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8700,16 +8700,16 @@
         <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.6</v>
+        <v>1.32</v>
       </c>
       <c r="M65" t="n">
-        <v>2.61</v>
+        <v>4.3</v>
       </c>
       <c r="N65" t="n">
-        <v>2.84</v>
+        <v>7.8</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8829,16 +8829,16 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.85</v>
+        <v>1.18</v>
       </c>
       <c r="M70" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="N70" t="n">
-        <v>3.95</v>
+        <v>12</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.28</v>
+        <v>1.95</v>
       </c>
       <c r="M71" t="n">
-        <v>5.3</v>
+        <v>2.96</v>
       </c>
       <c r="N71" t="n">
-        <v>12</v>
+        <v>3.71</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK72"/>
+  <dimension ref="A1:AK77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.83</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,16 +3030,16 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45894.55208333334</v>
+        <v>45894.54166666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45894.5625</v>
+        <v>45894.55208333334</v>
       </c>
     </row>
     <row r="25">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
       <c r="M27" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.5625</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="M28" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>3.19</v>
+        <v>4.33</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.5625</v>
       </c>
     </row>
     <row r="29">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="M29" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>3.91</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.5625</v>
       </c>
     </row>
     <row r="30">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="M30" t="n">
-        <v>3.29</v>
+        <v>3.06</v>
       </c>
       <c r="N30" t="n">
-        <v>3.1</v>
+        <v>3.61</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.79</v>
+        <v>2.07</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.1</v>
+        <v>2.36</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>1.69</v>
+        <v>2.61</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="M33" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="N33" t="n">
-        <v>2.79</v>
+        <v>2.91</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="N34" t="n">
-        <v>3.89</v>
+        <v>3.14</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>2.35</v>
+        <v>1.69</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="M36" t="n">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="N36" t="n">
-        <v>2.61</v>
+        <v>3.89</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="N37" t="n">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5401,27 +5401,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45894.60416666666</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="40">
@@ -5530,27 +5530,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.45</v>
+        <v>2.22</v>
       </c>
       <c r="M40" t="n">
-        <v>3.37</v>
+        <v>3.21</v>
       </c>
       <c r="N40" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45894.60416666666</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="44">
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="M44" t="n">
-        <v>4.6</v>
+        <v>3.37</v>
       </c>
       <c r="N44" t="n">
-        <v>4.05</v>
+        <v>2.74</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="45">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,19 +6670,19 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="49">
@@ -6691,27 +6691,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6777,10 +6777,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="52">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="53">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="54">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.43</v>
+        <v>6.7</v>
       </c>
       <c r="M54" t="n">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="N54" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,19 +7444,19 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45894.65625</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="55">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="M55" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N55" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="56">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7714,7 +7714,7 @@
         <v>0</v>
       </c>
       <c r="AK56" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="57">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="58">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.23</v>
+        <v>2.19</v>
       </c>
       <c r="M58" t="n">
-        <v>4.75</v>
+        <v>2.98</v>
       </c>
       <c r="N58" t="n">
-        <v>13.2</v>
+        <v>3.6</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="59">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.6</v>
+        <v>1.43</v>
       </c>
       <c r="M59" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="N59" t="n">
-        <v>1.92</v>
+        <v>6.8</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,16 +8061,16 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.65625</v>
       </c>
     </row>
     <row r="60">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.07</v>
+        <v>3.6</v>
       </c>
       <c r="M60" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N60" t="n">
-        <v>3.8</v>
+        <v>1.92</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,16 +8190,16 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="61">
@@ -8239,27 +8239,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="62">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="M62" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="N62" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="64">
@@ -8626,27 +8626,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.6</v>
+        <v>1.23</v>
       </c>
       <c r="M64" t="n">
-        <v>2.61</v>
+        <v>4.75</v>
       </c>
       <c r="N64" t="n">
-        <v>2.84</v>
+        <v>13.2</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8700,10 +8700,10 @@
         <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="65">
@@ -8755,27 +8755,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.32</v>
+        <v>2.07</v>
       </c>
       <c r="M65" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N65" t="n">
-        <v>7.8</v>
+        <v>3.8</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="66">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="67">
@@ -9013,27 +9013,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="M67" t="n">
-        <v>2.87</v>
+        <v>3.16</v>
       </c>
       <c r="N67" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9087,16 +9087,16 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="68">
@@ -9142,27 +9142,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="69">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.18</v>
+        <v>2.6</v>
       </c>
       <c r="M70" t="n">
-        <v>5.4</v>
+        <v>2.61</v>
       </c>
       <c r="N70" t="n">
-        <v>12</v>
+        <v>2.84</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9474,16 +9474,16 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="M71" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="N71" t="n">
-        <v>3.71</v>
+        <v>3.9</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="72">
@@ -9658,126 +9658,771 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>CSA</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M72" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N72" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X72" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK72" s="3" t="n">
+        <v>45894.8125</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Deportes Temuco</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M73" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N73" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3" t="n">
+        <v>45894.83333333334</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3" t="n">
+        <v>45894.83333333334</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Delfin SC</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M76" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N76" t="n">
+        <v>12</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="inlineStr">
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L72" t="n">
+      <c r="L77" t="n">
         <v>1.6</v>
       </c>
-      <c r="M72" t="n">
+      <c r="M77" t="n">
         <v>3.41</v>
       </c>
-      <c r="N72" t="n">
+      <c r="N77" t="n">
         <v>4.9</v>
       </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" t="n">
-        <v>0</v>
-      </c>
-      <c r="X72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y72" t="n">
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z72" t="n">
+      <c r="Z77" t="n">
         <v>1.58</v>
       </c>
-      <c r="AA72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK72" s="3" t="n">
+      <c r="AA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3" t="n">
         <v>45894.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,16 +2256,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="M22" t="n">
-        <v>3.83</v>
+        <v>2.99</v>
       </c>
       <c r="N22" t="n">
-        <v>3.47</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.16</v>
+        <v>3.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.47</v>
+        <v>1.83</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>2.93</v>
+        <v>4.33</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.83</v>
+        <v>2.47</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>4.33</v>
+        <v>2.93</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="M30" t="n">
-        <v>3.06</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
-        <v>3.61</v>
+        <v>3.1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="N32" t="n">
-        <v>2.61</v>
+        <v>3.19</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="M33" t="n">
-        <v>3.27</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>2.91</v>
+        <v>2.35</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.1</v>
+        <v>1.94</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.06</v>
       </c>
       <c r="N35" t="n">
-        <v>1.69</v>
+        <v>3.61</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="M36" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="N36" t="n">
-        <v>3.89</v>
+        <v>3.14</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="M37" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>3.19</v>
+        <v>2.61</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.34</v>
+        <v>1.68</v>
       </c>
       <c r="M38" t="n">
-        <v>3.01</v>
+        <v>3.74</v>
       </c>
       <c r="N38" t="n">
-        <v>2.78</v>
+        <v>3.89</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.71</v>
+        <v>2.32</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.54</v>
+        <v>2.34</v>
       </c>
       <c r="M39" t="n">
-        <v>3.95</v>
+        <v>3.01</v>
       </c>
       <c r="N39" t="n">
-        <v>4.6</v>
+        <v>2.78</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.36</v>
+        <v>2.02</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.9</v>
+        <v>1.71</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>3.27</v>
       </c>
       <c r="N41" t="n">
-        <v>2.35</v>
+        <v>2.91</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.03</v>
+        <v>1.54</v>
       </c>
       <c r="M42" t="n">
-        <v>3.29</v>
+        <v>3.95</v>
       </c>
       <c r="N42" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.79</v>
+        <v>2.9</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6777,10 +6777,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7035,10 +7035,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45894.63541666666</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,16 +7444,16 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45894.63541666666</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="M55" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="N55" t="n">
-        <v>2.86</v>
+        <v>3.6</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="M61" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="N61" t="n">
-        <v>3.86</v>
+        <v>3.2</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="M63" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="N63" t="n">
-        <v>3.2</v>
+        <v>3.86</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
       <c r="M69" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="N69" t="n">
-        <v>7.8</v>
+        <v>2.84</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9345,16 +9345,16 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.6</v>
+        <v>1.32</v>
       </c>
       <c r="M70" t="n">
-        <v>2.61</v>
+        <v>4.3</v>
       </c>
       <c r="N70" t="n">
-        <v>2.84</v>
+        <v>7.8</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9474,16 +9474,16 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.95</v>
+        <v>1.18</v>
       </c>
       <c r="M75" t="n">
-        <v>2.96</v>
+        <v>5.4</v>
       </c>
       <c r="N75" t="n">
-        <v>3.71</v>
+        <v>12</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.18</v>
+        <v>1.95</v>
       </c>
       <c r="M76" t="n">
-        <v>5.4</v>
+        <v>2.96</v>
       </c>
       <c r="N76" t="n">
-        <v>12</v>
+        <v>3.71</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK77"/>
+  <dimension ref="A1:AK75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="M22" t="n">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="O22" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.83</v>
+        <v>2.47</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>4.33</v>
+        <v>2.93</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>2.93</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45894.5625</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="29">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45894.5625</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="30">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.03</v>
+        <v>4.1</v>
       </c>
       <c r="M30" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>3.1</v>
+        <v>1.69</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.1</v>
+        <v>2.03</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="N31" t="n">
-        <v>1.69</v>
+        <v>3.1</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="M32" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>3.19</v>
+        <v>2.61</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.75</v>
+        <v>1.68</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>3.74</v>
       </c>
       <c r="N33" t="n">
-        <v>2.35</v>
+        <v>3.89</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="M35" t="n">
-        <v>3.06</v>
+        <v>3.21</v>
       </c>
       <c r="N35" t="n">
-        <v>3.61</v>
+        <v>2.79</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="M36" t="n">
-        <v>3.58</v>
+        <v>3.27</v>
       </c>
       <c r="N36" t="n">
-        <v>3.14</v>
+        <v>2.91</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,49 +5313,49 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1.68</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.54</v>
-      </c>
       <c r="Z38" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>3.01</v>
+        <v>3.28</v>
       </c>
       <c r="N39" t="n">
-        <v>2.78</v>
+        <v>3.19</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.22</v>
+        <v>1.54</v>
       </c>
       <c r="M40" t="n">
-        <v>3.21</v>
+        <v>3.95</v>
       </c>
       <c r="N40" t="n">
-        <v>2.79</v>
+        <v>4.6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.75</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5659,27 +5659,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="M41" t="n">
-        <v>3.27</v>
+        <v>3.37</v>
       </c>
       <c r="N41" t="n">
-        <v>2.91</v>
+        <v>2.74</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="42">
@@ -5788,27 +5788,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,27 +5917,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="M43" t="n">
-        <v>3.37</v>
+        <v>4.6</v>
       </c>
       <c r="N43" t="n">
-        <v>2.74</v>
+        <v>4.05</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45894.60416666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45894.60416666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="45">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,19 +6928,19 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="51">
@@ -6949,27 +6949,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7035,10 +7035,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="52">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45894.63541666666</v>
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="54">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="55">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.22</v>
+        <v>1.43</v>
       </c>
       <c r="M57" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N57" t="n">
-        <v>2.86</v>
+        <v>6.8</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.65625</v>
       </c>
     </row>
     <row r="58">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="59">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.43</v>
+        <v>2.26</v>
       </c>
       <c r="M59" t="n">
-        <v>4.5</v>
+        <v>3.18</v>
       </c>
       <c r="N59" t="n">
-        <v>6.8</v>
+        <v>2.93</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45894.65625</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="60">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.6</v>
+        <v>2.18</v>
       </c>
       <c r="M60" t="n">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="N60" t="n">
-        <v>1.92</v>
+        <v>3.25</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,16 +8190,16 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.35</v>
+        <v>1.55</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="M61" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="N61" t="n">
-        <v>3.2</v>
+        <v>1.92</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,16 +8319,16 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="M62" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>2.93</v>
+        <v>4</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8497,27 +8497,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="64">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.23</v>
+        <v>2.07</v>
       </c>
       <c r="M64" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>13.2</v>
+        <v>3.8</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="65">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.07</v>
+        <v>2.35</v>
       </c>
       <c r="M65" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="N65" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="66">
@@ -8884,27 +8884,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="67">
@@ -9013,27 +9013,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="68">
@@ -9142,27 +9142,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="M68" t="n">
-        <v>3.16</v>
+        <v>2.61</v>
       </c>
       <c r="N68" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9216,16 +9216,16 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="69">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="M69" t="n">
-        <v>2.61</v>
+        <v>2.87</v>
       </c>
       <c r="N69" t="n">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9345,10 +9345,10 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="X69" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Y69" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.32</v>
+        <v>1.85</v>
       </c>
       <c r="M70" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="N70" t="n">
-        <v>7.8</v>
+        <v>3.9</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.83333333334</v>
       </c>
     </row>
     <row r="72">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="M72" t="n">
-        <v>2.87</v>
+        <v>3.16</v>
       </c>
       <c r="N72" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9732,16 +9732,16 @@
         <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.83333333334</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.875</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.25</v>
+        <v>1.18</v>
       </c>
       <c r="M74" t="n">
-        <v>3.16</v>
+        <v>5.4</v>
       </c>
       <c r="N74" t="n">
-        <v>2.8</v>
+        <v>12</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.875</v>
       </c>
     </row>
     <row r="75">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="M75" t="n">
-        <v>5.4</v>
+        <v>3.41</v>
       </c>
       <c r="N75" t="n">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10165,264 +10165,6 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45894.875</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
-        <v>45894</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Orense SC</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Delfin SC</t>
-        </is>
-      </c>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L76" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M76" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="N76" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" t="n">
-        <v>0</v>
-      </c>
-      <c r="W76" t="n">
-        <v>0</v>
-      </c>
-      <c r="X76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK76" s="3" t="n">
-        <v>45894.875</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
-        <v>45894</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L77" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M77" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="N77" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" t="n">
-        <v>0</v>
-      </c>
-      <c r="W77" t="n">
-        <v>0</v>
-      </c>
-      <c r="X77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK77" s="3" t="n">
         <v>45894.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,16 +2256,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,16 +2385,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2991,43 +2991,43 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y20" t="n">
         <v>2.25</v>
@@ -3036,16 +3036,16 @@
         <v>1.65</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Z25" t="n">
         <v>1.7</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Z26" t="n">
         <v>1.7</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.01</v>
       </c>
       <c r="N28" t="n">
-        <v>2.35</v>
+        <v>2.78</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.34</v>
+        <v>4.1</v>
       </c>
       <c r="M29" t="n">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>2.78</v>
+        <v>1.69</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.1</v>
+        <v>1.68</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="N30" t="n">
-        <v>1.69</v>
+        <v>3.89</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.03</v>
+        <v>1.54</v>
       </c>
       <c r="M31" t="n">
-        <v>3.29</v>
+        <v>3.95</v>
       </c>
       <c r="N31" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.79</v>
+        <v>2.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.36</v>
+        <v>2.03</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="N32" t="n">
-        <v>2.61</v>
+        <v>3.1</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.68</v>
+        <v>2.36</v>
       </c>
       <c r="M33" t="n">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>3.89</v>
+        <v>2.61</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="N34" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="M35" t="n">
-        <v>3.21</v>
+        <v>3.06</v>
       </c>
       <c r="N35" t="n">
-        <v>2.79</v>
+        <v>3.61</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="M36" t="n">
-        <v>3.27</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>2.91</v>
+        <v>2.35</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.94</v>
+        <v>2.13</v>
       </c>
       <c r="M38" t="n">
-        <v>3.06</v>
+        <v>3.27</v>
       </c>
       <c r="N38" t="n">
-        <v>3.61</v>
+        <v>2.91</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="M39" t="n">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="N39" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.65</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.54</v>
+        <v>2.22</v>
       </c>
       <c r="M40" t="n">
-        <v>3.95</v>
+        <v>3.21</v>
       </c>
       <c r="N40" t="n">
-        <v>4.6</v>
+        <v>2.79</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6003,10 +6003,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.23</v>
+        <v>3.6</v>
       </c>
       <c r="M58" t="n">
-        <v>4.75</v>
+        <v>3.95</v>
       </c>
       <c r="N58" t="n">
-        <v>13.2</v>
+        <v>1.92</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,16 +7932,16 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="M61" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N61" t="n">
-        <v>1.92</v>
+        <v>4</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,16 +8319,16 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.35</v>
+        <v>1.55</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.9</v>
+        <v>1.23</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="N62" t="n">
-        <v>4</v>
+        <v>13.2</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="N10" t="n">
-        <v>5.72</v>
+        <v>6.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,16 +2256,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,16 +2385,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.92</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="N25" t="n">
-        <v>3.91</v>
+        <v>2.85</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Z26" t="n">
         <v>1.7</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.47</v>
+        <v>1.93</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>2.93</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.34</v>
+        <v>1.92</v>
       </c>
       <c r="M28" t="n">
-        <v>3.01</v>
+        <v>3.58</v>
       </c>
       <c r="N28" t="n">
-        <v>2.78</v>
+        <v>3.14</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="M30" t="n">
-        <v>3.74</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
-        <v>3.89</v>
+        <v>3.1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="N32" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.01</v>
       </c>
       <c r="N33" t="n">
-        <v>2.61</v>
+        <v>2.78</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="M34" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="N34" t="n">
-        <v>3.19</v>
+        <v>2.91</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.94</v>
+        <v>1.54</v>
       </c>
       <c r="M35" t="n">
-        <v>3.06</v>
+        <v>3.95</v>
       </c>
       <c r="N35" t="n">
-        <v>3.61</v>
+        <v>4.6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.75</v>
+        <v>2.22</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="N36" t="n">
-        <v>2.35</v>
+        <v>2.79</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="M38" t="n">
-        <v>3.27</v>
+        <v>3.06</v>
       </c>
       <c r="N38" t="n">
-        <v>2.91</v>
+        <v>3.61</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.92</v>
+        <v>2.36</v>
       </c>
       <c r="M39" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>3.14</v>
+        <v>2.61</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.22</v>
+        <v>2.75</v>
       </c>
       <c r="M40" t="n">
-        <v>3.21</v>
+        <v>3.45</v>
       </c>
       <c r="N40" t="n">
-        <v>2.79</v>
+        <v>2.35</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6648,10 +6648,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.6</v>
+        <v>1.23</v>
       </c>
       <c r="M58" t="n">
-        <v>3.95</v>
+        <v>4.75</v>
       </c>
       <c r="N58" t="n">
-        <v>1.92</v>
+        <v>13.2</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,16 +7932,16 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="M59" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="N59" t="n">
-        <v>2.93</v>
+        <v>4</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.18</v>
+        <v>3.6</v>
       </c>
       <c r="M60" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="N60" t="n">
-        <v>3.25</v>
+        <v>1.92</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,16 +8190,16 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="M61" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="N61" t="n">
-        <v>4</v>
+        <v>2.93</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.23</v>
+        <v>2.18</v>
       </c>
       <c r="M62" t="n">
-        <v>4.75</v>
+        <v>3.15</v>
       </c>
       <c r="N62" t="n">
-        <v>13.2</v>
+        <v>3.25</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
       <c r="M67" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="N67" t="n">
-        <v>7.8</v>
+        <v>2.84</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9087,16 +9087,16 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.6</v>
+        <v>1.32</v>
       </c>
       <c r="M68" t="n">
-        <v>2.61</v>
+        <v>4.3</v>
       </c>
       <c r="N68" t="n">
-        <v>2.84</v>
+        <v>7.8</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9216,16 +9216,16 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="M69" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="N69" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9345,16 +9345,16 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="M70" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="N70" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9474,16 +9474,16 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK75"/>
+  <dimension ref="A1:AK77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="M21" t="n">
-        <v>3.83</v>
+        <v>3.11</v>
       </c>
       <c r="N21" t="n">
-        <v>3.47</v>
+        <v>3.02</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.11</v>
+        <v>3.83</v>
       </c>
       <c r="N22" t="n">
-        <v>3.02</v>
+        <v>3.47</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4026,10 +4026,10 @@
         <v>1.92</v>
       </c>
       <c r="M28" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.14</v>
+        <v>3.91</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.5625</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.5625</v>
       </c>
     </row>
     <row r="30">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="M30" t="n">
-        <v>3.29</v>
+        <v>3.21</v>
       </c>
       <c r="N30" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="M32" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>3.19</v>
+        <v>2.61</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.34</v>
+        <v>2.03</v>
       </c>
       <c r="M33" t="n">
-        <v>3.01</v>
+        <v>3.29</v>
       </c>
       <c r="N33" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.13</v>
+        <v>4.1</v>
       </c>
       <c r="M34" t="n">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.91</v>
+        <v>1.69</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.54</v>
+        <v>1.94</v>
       </c>
       <c r="M35" t="n">
-        <v>3.95</v>
+        <v>3.06</v>
       </c>
       <c r="N35" t="n">
-        <v>4.6</v>
+        <v>3.61</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.22</v>
+        <v>2.75</v>
       </c>
       <c r="M36" t="n">
-        <v>3.21</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>2.79</v>
+        <v>2.35</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.68</v>
+        <v>2.13</v>
       </c>
       <c r="M37" t="n">
-        <v>3.74</v>
+        <v>3.27</v>
       </c>
       <c r="N37" t="n">
-        <v>3.89</v>
+        <v>2.91</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>3.01</v>
       </c>
       <c r="N39" t="n">
-        <v>2.61</v>
+        <v>2.78</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.75</v>
+        <v>1.92</v>
       </c>
       <c r="M40" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="N40" t="n">
-        <v>2.35</v>
+        <v>3.14</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5659,27 +5659,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45894.60416666666</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="N42" t="n">
-        <v>2.74</v>
+        <v>3.19</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45894.60416666666</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="45">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6648,10 +6648,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6777,10 +6777,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,19 +6928,19 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="52">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="54">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,19 +7444,19 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="55">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.43</v>
+        <v>2.22</v>
       </c>
       <c r="M57" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N57" t="n">
-        <v>6.8</v>
+        <v>2.86</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45894.65625</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="58">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.23</v>
+        <v>2.19</v>
       </c>
       <c r="M58" t="n">
-        <v>4.75</v>
+        <v>2.98</v>
       </c>
       <c r="N58" t="n">
-        <v>13.2</v>
+        <v>3.6</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="59">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.9</v>
+        <v>1.43</v>
       </c>
       <c r="M59" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N59" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.65625</v>
       </c>
     </row>
     <row r="60">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.07</v>
+        <v>1.23</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="N63" t="n">
-        <v>3.8</v>
+        <v>13.2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="64">
@@ -8626,27 +8626,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="65">
@@ -8755,27 +8755,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="66">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="67">
@@ -9013,27 +9013,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="M67" t="n">
-        <v>2.61</v>
+        <v>3.16</v>
       </c>
       <c r="N67" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9087,16 +9087,16 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="68">
@@ -9142,27 +9142,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="69">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="M69" t="n">
-        <v>3.1</v>
+        <v>2.61</v>
       </c>
       <c r="N69" t="n">
-        <v>3.9</v>
+        <v>2.84</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9345,16 +9345,16 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.1</v>
+        <v>1.32</v>
       </c>
       <c r="M70" t="n">
-        <v>2.87</v>
+        <v>4.3</v>
       </c>
       <c r="N70" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9474,16 +9474,16 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9603,10 +9603,10 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="72">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,49 +9699,49 @@
         </is>
       </c>
       <c r="L72" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M72" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N72" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="n">
         <v>2.25</v>
       </c>
-      <c r="M72" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N72" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" t="n">
-        <v>0</v>
-      </c>
-      <c r="X72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Z72" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="M73" t="n">
-        <v>2.96</v>
+        <v>3.16</v>
       </c>
       <c r="N73" t="n">
-        <v>3.71</v>
+        <v>2.8</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.83333333334</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.83333333334</v>
       </c>
     </row>
     <row r="75">
@@ -10045,126 +10045,384 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Delfin SC</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M76" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N76" t="n">
+        <v>12</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="inlineStr">
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L75" t="n">
+      <c r="L77" t="n">
         <v>1.6</v>
       </c>
-      <c r="M75" t="n">
+      <c r="M77" t="n">
         <v>3.41</v>
       </c>
-      <c r="N75" t="n">
+      <c r="N77" t="n">
         <v>4.9</v>
       </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" t="n">
-        <v>0</v>
-      </c>
-      <c r="V75" t="n">
-        <v>0</v>
-      </c>
-      <c r="W75" t="n">
-        <v>0</v>
-      </c>
-      <c r="X75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y75" t="n">
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z75" t="n">
+      <c r="Z77" t="n">
         <v>1.58</v>
       </c>
-      <c r="AA75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK75" s="3" t="n">
+      <c r="AA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3" t="n">
         <v>45894.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>9.5</v>
+        <v>3.65</v>
       </c>
       <c r="M13" t="n">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="N13" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.65</v>
+        <v>9.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,16 +2256,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.11</v>
+        <v>3.83</v>
       </c>
       <c r="N21" t="n">
-        <v>3.02</v>
+        <v>3.47</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="M22" t="n">
-        <v>3.83</v>
+        <v>3.11</v>
       </c>
       <c r="N22" t="n">
-        <v>3.47</v>
+        <v>3.02</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>1.92</v>
       </c>
       <c r="M25" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.85</v>
+        <v>3.91</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Z28" t="n">
         <v>1.7</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4185,10 +4185,10 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="N30" t="n">
-        <v>2.79</v>
+        <v>3.19</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="Z30" t="n">
         <v>2.1</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.68</v>
+        <v>2.22</v>
       </c>
       <c r="M31" t="n">
-        <v>3.74</v>
+        <v>3.21</v>
       </c>
       <c r="N31" t="n">
-        <v>3.89</v>
+        <v>2.79</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.03</v>
+        <v>1.54</v>
       </c>
       <c r="M33" t="n">
-        <v>3.29</v>
+        <v>3.95</v>
       </c>
       <c r="N33" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.79</v>
+        <v>2.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.1</v>
+        <v>2.03</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="N34" t="n">
-        <v>1.69</v>
+        <v>3.1</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="M35" t="n">
-        <v>3.06</v>
+        <v>3.58</v>
       </c>
       <c r="N35" t="n">
-        <v>3.61</v>
+        <v>3.14</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.35</v>
+        <v>1.69</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.13</v>
+        <v>1.68</v>
       </c>
       <c r="M37" t="n">
-        <v>3.27</v>
+        <v>3.74</v>
       </c>
       <c r="N37" t="n">
-        <v>2.91</v>
+        <v>3.89</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="M40" t="n">
-        <v>3.58</v>
+        <v>3.06</v>
       </c>
       <c r="N40" t="n">
-        <v>3.14</v>
+        <v>3.61</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.54</v>
+        <v>2.34</v>
       </c>
       <c r="M41" t="n">
-        <v>3.95</v>
+        <v>3.01</v>
       </c>
       <c r="N41" t="n">
-        <v>4.6</v>
+        <v>2.78</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="M42" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="N42" t="n">
-        <v>3.19</v>
+        <v>2.61</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.77</v>
+        <v>2.45</v>
       </c>
       <c r="M44" t="n">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
       <c r="N44" t="n">
-        <v>4.6</v>
+        <v>2.74</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6648,10 +6648,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6777,10 +6777,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45894.63541666666</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,16 +7444,16 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45894.63541666666</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.6</v>
+        <v>1.23</v>
       </c>
       <c r="M60" t="n">
-        <v>3.95</v>
+        <v>4.75</v>
       </c>
       <c r="N60" t="n">
-        <v>1.92</v>
+        <v>13.2</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,16 +8190,16 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="M61" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="N61" t="n">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.18</v>
+        <v>3.6</v>
       </c>
       <c r="M62" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="N62" t="n">
-        <v>3.25</v>
+        <v>1.92</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,16 +8476,16 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AK62" s="3" t="n">
         <v>45894.66666666666</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.23</v>
+        <v>1.9</v>
       </c>
       <c r="M63" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>13.2</v>
+        <v>4</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="N64" t="n">
-        <v>4</v>
+        <v>2.93</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.6</v>
+        <v>1.32</v>
       </c>
       <c r="M69" t="n">
-        <v>2.61</v>
+        <v>4.3</v>
       </c>
       <c r="N69" t="n">
-        <v>2.84</v>
+        <v>7.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9345,16 +9345,16 @@
         <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
       <c r="M70" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="N70" t="n">
-        <v>7.8</v>
+        <v>2.84</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9474,16 +9474,16 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="M71" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="N71" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9603,16 +9603,16 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="M72" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="N72" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9732,16 +9732,16 @@
         <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.95</v>
+        <v>1.18</v>
       </c>
       <c r="M75" t="n">
-        <v>2.96</v>
+        <v>5.4</v>
       </c>
       <c r="N75" t="n">
-        <v>3.71</v>
+        <v>12</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.18</v>
+        <v>1.95</v>
       </c>
       <c r="M76" t="n">
-        <v>5.4</v>
+        <v>2.96</v>
       </c>
       <c r="N76" t="n">
-        <v>12</v>
+        <v>3.71</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK77"/>
+  <dimension ref="A1:AK79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,16 +1998,16 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>9.5</v>
+        <v>2.9</v>
       </c>
       <c r="M14" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,16 +2250,16 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.9</v>
+        <v>9.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,16 +2379,16 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45894.52083333334</v>
+        <v>45894.5</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45894.53125</v>
+        <v>45894.5</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45894.53125</v>
+        <v>45894.52083333334</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45894.54166666666</v>
+        <v>45894.53125</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45894.54166666666</v>
+        <v>45894.53125</v>
       </c>
     </row>
     <row r="22">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="M22" t="n">
-        <v>3.11</v>
+        <v>2.99</v>
       </c>
       <c r="N22" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45894.55208333334</v>
+        <v>45894.54166666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.83</v>
       </c>
       <c r="N25" t="n">
-        <v>3.91</v>
+        <v>3.47</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45894.5625</v>
+        <v>45894.54166666666</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45894.5625</v>
+        <v>45894.55208333334</v>
       </c>
     </row>
     <row r="27">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.5625</v>
       </c>
     </row>
     <row r="31">
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="M31" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>2.79</v>
+        <v>3.91</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.5625</v>
       </c>
     </row>
     <row r="32">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.75</v>
+        <v>1.92</v>
       </c>
       <c r="M32" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="N32" t="n">
-        <v>2.35</v>
+        <v>3.14</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.54</v>
+        <v>2.22</v>
       </c>
       <c r="M33" t="n">
-        <v>3.95</v>
+        <v>3.21</v>
       </c>
       <c r="N33" t="n">
-        <v>4.6</v>
+        <v>2.79</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.03</v>
+        <v>1.54</v>
       </c>
       <c r="M34" t="n">
-        <v>3.29</v>
+        <v>3.95</v>
       </c>
       <c r="N34" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.79</v>
+        <v>2.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.92</v>
+        <v>2.75</v>
       </c>
       <c r="M35" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>3.14</v>
+        <v>2.35</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.1</v>
+        <v>2.13</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="N36" t="n">
-        <v>1.69</v>
+        <v>2.91</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="M37" t="n">
-        <v>3.74</v>
+        <v>3.29</v>
       </c>
       <c r="N37" t="n">
-        <v>3.89</v>
+        <v>3.1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="M40" t="n">
-        <v>3.06</v>
+        <v>3.81</v>
       </c>
       <c r="N40" t="n">
-        <v>3.61</v>
+        <v>4</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="M41" t="n">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="N41" t="n">
-        <v>2.78</v>
+        <v>2.61</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="N42" t="n">
-        <v>2.61</v>
+        <v>3.19</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5917,27 +5917,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45894.60416666666</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="44">
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="M44" t="n">
-        <v>3.37</v>
+        <v>3.01</v>
       </c>
       <c r="N44" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45894.60416666666</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="47">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6648,10 +6648,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7078,27 +7078,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>6.7</v>
+        <v>1.7</v>
       </c>
       <c r="M52" t="n">
-        <v>3.94</v>
+        <v>4.6</v>
       </c>
       <c r="N52" t="n">
-        <v>1.4</v>
+        <v>4.05</v>
       </c>
       <c r="O52" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB52" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q52" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S52" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X52" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AC52" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,19 +7186,19 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="53">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="54">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.22</v>
+        <v>6.7</v>
       </c>
       <c r="M55" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O55" t="n">
+        <v>6</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X55" t="n">
         <v>3.3</v>
       </c>
-      <c r="N55" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
       <c r="Y55" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,19 +7573,19 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="56">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7714,7 +7714,7 @@
         <v>0</v>
       </c>
       <c r="AK56" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="57">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.43</v>
+        <v>2.22</v>
       </c>
       <c r="M59" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N59" t="n">
-        <v>6.8</v>
+        <v>2.86</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45894.65625</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="60">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="61">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.18</v>
+        <v>1.43</v>
       </c>
       <c r="M61" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="N61" t="n">
-        <v>3.25</v>
+        <v>6.8</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.65625</v>
       </c>
     </row>
     <row r="62">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.6</v>
+        <v>2.26</v>
       </c>
       <c r="M62" t="n">
-        <v>3.95</v>
+        <v>3.18</v>
       </c>
       <c r="N62" t="n">
-        <v>1.92</v>
+        <v>2.93</v>
       </c>
       <c r="O62" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,16 +8476,16 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
         <v>45894.66666666666</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N63" t="n">
-        <v>4</v>
+        <v>1.92</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,16 +8605,16 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI63" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45894.66666666666</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="M64" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>2.93</v>
+        <v>4</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8755,27 +8755,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="66">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="M66" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N66" t="n">
         <v>3.25</v>
-      </c>
-      <c r="N66" t="n">
-        <v>3.8</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8967,7 +8967,7 @@
         <v>2.3</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="67">
@@ -9013,27 +9013,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="68">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="M68" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="69">
@@ -9271,27 +9271,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.32</v>
+        <v>2.35</v>
       </c>
       <c r="M69" t="n">
-        <v>4.3</v>
+        <v>3.16</v>
       </c>
       <c r="N69" t="n">
-        <v>7.8</v>
+        <v>3.05</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="70">
@@ -9400,27 +9400,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="M70" t="n">
-        <v>2.61</v>
+        <v>3.2</v>
       </c>
       <c r="N70" t="n">
-        <v>2.84</v>
+        <v>3.52</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9474,16 +9474,16 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="M71" t="n">
-        <v>3.1</v>
+        <v>2.61</v>
       </c>
       <c r="N71" t="n">
-        <v>3.9</v>
+        <v>2.84</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9603,16 +9603,16 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="72">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.1</v>
+        <v>1.32</v>
       </c>
       <c r="M72" t="n">
-        <v>2.87</v>
+        <v>4.3</v>
       </c>
       <c r="N72" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9732,16 +9732,16 @@
         <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,49 +9828,49 @@
         </is>
       </c>
       <c r="L73" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M73" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N73" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="n">
         <v>2.25</v>
       </c>
-      <c r="M73" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N73" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" t="n">
-        <v>0</v>
-      </c>
-      <c r="W73" t="n">
-        <v>0</v>
-      </c>
-      <c r="X73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Z73" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9990,10 +9990,10 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="75">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.83333333334</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="M76" t="n">
-        <v>2.96</v>
+        <v>3.16</v>
       </c>
       <c r="N76" t="n">
-        <v>3.71</v>
+        <v>2.8</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.83333333334</v>
       </c>
     </row>
     <row r="77">
@@ -10303,126 +10303,384 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M77" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N77" t="n">
+        <v>12</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Delfin SC</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M78" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N78" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK78" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="inlineStr">
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L77" t="n">
+      <c r="L79" t="n">
         <v>1.6</v>
       </c>
-      <c r="M77" t="n">
+      <c r="M79" t="n">
         <v>3.41</v>
       </c>
-      <c r="N77" t="n">
+      <c r="N79" t="n">
         <v>4.9</v>
       </c>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" t="n">
-        <v>0</v>
-      </c>
-      <c r="W77" t="n">
-        <v>0</v>
-      </c>
-      <c r="X77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y77" t="n">
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z77" t="n">
+      <c r="Z79" t="n">
         <v>1.58</v>
       </c>
-      <c r="AA77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK77" s="3" t="n">
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK79" s="3" t="n">
         <v>45894.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK79"/>
+  <dimension ref="A1:AK81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,16 +1998,16 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,16 +2643,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2766,10 +2766,10 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.22</v>
+        <v>2.95</v>
       </c>
       <c r="M22" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>2.23</v>
       </c>
       <c r="O22" t="n">
-        <v>2.97</v>
+        <v>2.54</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>2.58</v>
+        <v>2.85</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V22" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="X22" t="n">
-        <v>2.79</v>
+        <v>3.14</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.88</v>
+        <v>3.28</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45894.55208333334</v>
+        <v>45894.54166666666</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45894.5625</v>
+        <v>45894.55208333334</v>
       </c>
     </row>
     <row r="28">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4185,10 +4185,10 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.92</v>
+        <v>2.8</v>
       </c>
       <c r="M32" t="n">
-        <v>3.58</v>
+        <v>2.7</v>
       </c>
       <c r="N32" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4572,22 +4572,22 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45894.58333333334</v>
+        <v>45894.5625</v>
       </c>
     </row>
     <row r="33">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.54</v>
+        <v>2.03</v>
       </c>
       <c r="M34" t="n">
-        <v>3.95</v>
+        <v>3.29</v>
       </c>
       <c r="N34" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.9</v>
+        <v>1.79</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>2.35</v>
+        <v>1.69</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.13</v>
+        <v>1.54</v>
       </c>
       <c r="M36" t="n">
-        <v>3.27</v>
+        <v>3.95</v>
       </c>
       <c r="N36" t="n">
-        <v>2.91</v>
+        <v>4.6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="M37" t="n">
-        <v>3.29</v>
+        <v>3.21</v>
       </c>
       <c r="N37" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.1</v>
+        <v>2.36</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>1.69</v>
+        <v>2.61</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="M40" t="n">
-        <v>3.81</v>
+        <v>3.58</v>
       </c>
       <c r="N40" t="n">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA40" t="n">
         <v>2.25</v>
       </c>
-      <c r="P40" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>4</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X40" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AB40" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="N41" t="n">
-        <v>2.61</v>
+        <v>3.19</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="M42" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="N42" t="n">
-        <v>3.19</v>
+        <v>2.91</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="M43" t="n">
-        <v>3.06</v>
+        <v>3.74</v>
       </c>
       <c r="N43" t="n">
-        <v>3.61</v>
+        <v>3.89</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.34</v>
+        <v>1.94</v>
       </c>
       <c r="M44" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="N44" t="n">
-        <v>2.78</v>
+        <v>3.61</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="M45" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="N45" t="n">
-        <v>2.74</v>
+        <v>2.35</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45894.60416666666</v>
+        <v>45894.58333333334</v>
       </c>
     </row>
     <row r="46">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45894.625</v>
+        <v>45894.60416666666</v>
       </c>
     </row>
     <row r="48">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7035,10 +7035,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7164,10 +7164,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45894.63541666666</v>
+        <v>45894.625</v>
       </c>
     </row>
     <row r="55">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45894.64583333334</v>
+        <v>45894.63541666666</v>
       </c>
     </row>
     <row r="58">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45894.65625</v>
+        <v>45894.64583333334</v>
       </c>
     </row>
     <row r="62">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,34 +8409,34 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.26</v>
+        <v>3.27</v>
       </c>
       <c r="M62" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>2.93</v>
+        <v>1.97</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8460,10 +8460,10 @@
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8482,13 +8482,13 @@
         <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.65625</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.6</v>
+        <v>1.43</v>
       </c>
       <c r="M63" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="N63" t="n">
-        <v>1.92</v>
+        <v>6.8</v>
       </c>
       <c r="O63" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z63" t="n">
         <v>2.15</v>
       </c>
-      <c r="U63" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V63" t="n">
-        <v>1</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X63" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AA63" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,19 +8605,19 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AJ63" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45894.66666666666</v>
+        <v>45894.65625</v>
       </c>
     </row>
     <row r="64">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="N64" t="n">
-        <v>4</v>
+        <v>2.93</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.23</v>
+        <v>1.9</v>
       </c>
       <c r="M65" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="N65" t="n">
-        <v>13.2</v>
+        <v>4</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -9013,27 +9013,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="68">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.07</v>
+        <v>3.6</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N68" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O68" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P68" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S68" t="n">
         <v>3.8</v>
       </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,19 +9250,19 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45894.67708333334</v>
+        <v>45894.66666666666</v>
       </c>
     </row>
     <row r="69">
@@ -9271,27 +9271,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.29</v>
+        <v>2.07</v>
       </c>
       <c r="M70" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N70" t="n">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45894.6875</v>
+        <v>45894.67708333334</v>
       </c>
     </row>
     <row r="71">
@@ -9529,27 +9529,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="M71" t="n">
-        <v>2.61</v>
+        <v>3.2</v>
       </c>
       <c r="N71" t="n">
-        <v>2.84</v>
+        <v>3.52</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9603,16 +9603,16 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="72">
@@ -9658,27 +9658,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.32</v>
+        <v>2.35</v>
       </c>
       <c r="M72" t="n">
-        <v>4.3</v>
+        <v>3.16</v>
       </c>
       <c r="N72" t="n">
-        <v>7.8</v>
+        <v>3.05</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45894.79166666666</v>
+        <v>45894.6875</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.85</v>
+        <v>1.32</v>
       </c>
       <c r="M73" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="N73" t="n">
-        <v>3.9</v>
+        <v>7.8</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="M74" t="n">
-        <v>2.87</v>
+        <v>2.61</v>
       </c>
       <c r="N74" t="n">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9990,10 +9990,10 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="X74" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Y74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45894.8125</v>
+        <v>45894.79166666666</v>
       </c>
     </row>
     <row r="75">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10119,10 +10119,10 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y75" t="n">
         <v>0</v>
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,49 +10215,49 @@
         </is>
       </c>
       <c r="L76" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M76" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
         <v>2.25</v>
       </c>
-      <c r="M76" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N76" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" t="n">
-        <v>0</v>
-      </c>
-      <c r="W76" t="n">
-        <v>0</v>
-      </c>
-      <c r="X76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Z76" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.8125</v>
       </c>
     </row>
     <row r="77">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.83333333334</v>
       </c>
     </row>
     <row r="78">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="M78" t="n">
-        <v>2.96</v>
+        <v>3.16</v>
       </c>
       <c r="N78" t="n">
-        <v>3.71</v>
+        <v>2.8</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>45894.875</v>
+        <v>45894.83333333334</v>
       </c>
     </row>
     <row r="79">
@@ -10561,126 +10561,384 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Delfin SC</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N79" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK79" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M80" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N80" t="n">
+        <v>12</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK80" s="3" t="n">
+        <v>45894.875</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Amazonas</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="inlineStr">
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L79" t="n">
+      <c r="L81" t="n">
         <v>1.6</v>
       </c>
-      <c r="M79" t="n">
+      <c r="M81" t="n">
         <v>3.41</v>
       </c>
-      <c r="N79" t="n">
+      <c r="N81" t="n">
         <v>4.9</v>
       </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y79" t="n">
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z79" t="n">
+      <c r="Z81" t="n">
         <v>1.58</v>
       </c>
-      <c r="AA79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK79" s="3" t="n">
+      <c r="AA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK81" s="3" t="n">
         <v>45894.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK81"/>
+  <dimension ref="A1:AK80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,16 +2379,16 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,16 +2643,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.74</v>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2766,22 +2766,22 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AA18" t="n">
         <v>2.35</v>
       </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P26" t="n">
         <v>2.14</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="N28" t="n">
-        <v>4.1</v>
+        <v>2.85</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4056,16 +4056,16 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.8</v>
+        <v>1.92</v>
       </c>
       <c r="M32" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>2.85</v>
+        <v>3.91</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4572,16 +4572,16 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="M34" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="N34" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.1</v>
+        <v>1.94</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.06</v>
       </c>
       <c r="N35" t="n">
-        <v>1.69</v>
+        <v>3.61</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.54</v>
+        <v>4.1</v>
       </c>
       <c r="M36" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>4.6</v>
+        <v>1.69</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.9</v>
+        <v>1.89</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.22</v>
+        <v>1.54</v>
       </c>
       <c r="M37" t="n">
-        <v>3.21</v>
+        <v>3.95</v>
       </c>
       <c r="N37" t="n">
-        <v>2.79</v>
+        <v>4.6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB37" t="n">
         <v>1.75</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5322,34 +5322,34 @@
         <v>2.78</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y38" t="n">
         <v>2.2</v>
@@ -5358,16 +5358,16 @@
         <v>1.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="N39" t="n">
-        <v>2.61</v>
+        <v>2.79</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="M40" t="n">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="N40" t="n">
-        <v>3.14</v>
+        <v>3.89</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="M41" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>3.19</v>
+        <v>2.35</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.13</v>
+        <v>2.36</v>
       </c>
       <c r="M42" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="N42" t="n">
-        <v>2.91</v>
+        <v>2.61</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="M43" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="N43" t="n">
-        <v>3.89</v>
+        <v>3.14</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="M44" t="n">
-        <v>3.06</v>
+        <v>3.29</v>
       </c>
       <c r="N44" t="n">
-        <v>3.61</v>
+        <v>3.1</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N45" t="n">
-        <v>2.35</v>
+        <v>3.19</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7035,10 +7035,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,16 +7573,16 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45894.63541666666</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,16 +7831,16 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45894.63541666666</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.27</v>
+        <v>3.45</v>
       </c>
       <c r="M62" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N62" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="O62" t="n">
         <v>4.33</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="M64" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="M65" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N65" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,7 +8835,7 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z65" t="n">
         <v>1.55</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,61 +8925,61 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.18</v>
+        <v>3.6</v>
       </c>
       <c r="M66" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="N66" t="n">
-        <v>3.25</v>
+        <v>1.92</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -8992,16 +8992,16 @@
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI66" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45894.66666666666</v>
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M67" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="N67" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="M68" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>1.92</v>
+        <v>4</v>
       </c>
       <c r="O68" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.35</v>
+        <v>1.55</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,16 +9250,16 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AJ68" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
         <v>45894.66666666666</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="M71" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="N71" t="n">
-        <v>3.52</v>
+        <v>3.05</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
       <c r="M73" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="N73" t="n">
-        <v>7.8</v>
+        <v>2.84</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9861,16 +9861,16 @@
         <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.6</v>
+        <v>1.32</v>
       </c>
       <c r="M74" t="n">
-        <v>2.61</v>
+        <v>4.3</v>
       </c>
       <c r="N74" t="n">
-        <v>2.84</v>
+        <v>7.8</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9990,16 +9990,16 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="M75" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="N75" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10119,10 +10119,10 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X75" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Y75" t="n">
         <v>0</v>
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="M76" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N76" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10432,12 +10432,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="M78" t="n">
-        <v>3.16</v>
+        <v>2.96</v>
       </c>
       <c r="N78" t="n">
-        <v>2.8</v>
+        <v>3.71</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>45894.83333333334</v>
+        <v>45894.875</v>
       </c>
     </row>
     <row r="79">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.95</v>
+        <v>1.18</v>
       </c>
       <c r="M79" t="n">
-        <v>2.96</v>
+        <v>5.4</v>
       </c>
       <c r="N79" t="n">
-        <v>3.71</v>
+        <v>12</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10690,12 +10690,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="M80" t="n">
-        <v>5.4</v>
+        <v>3.41</v>
       </c>
       <c r="N80" t="n">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10810,135 +10810,6 @@
         <v>0</v>
       </c>
       <c r="AK80" s="3" t="n">
-        <v>45894.875</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>45894</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Amazonas</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L81" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M81" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="N81" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" t="n">
-        <v>0</v>
-      </c>
-      <c r="V81" t="n">
-        <v>0</v>
-      </c>
-      <c r="W81" t="n">
-        <v>0</v>
-      </c>
-      <c r="X81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK81" s="3" t="n">
         <v>45894.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -936,40 +936,40 @@
         <v>7.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>6.64</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="n">
         <v>1.95</v>
@@ -978,10 +978,10 @@
         <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8.4</v>
+        <v>3.65</v>
       </c>
       <c r="M14" t="n">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="N14" t="n">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,16 +2256,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,16 +2772,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.74</v>
+        <v>2.14</v>
       </c>
       <c r="M26" t="n">
-        <v>3.23</v>
+        <v>3.11</v>
       </c>
       <c r="N26" t="n">
-        <v>2.24</v>
+        <v>3.02</v>
       </c>
       <c r="O26" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4056,10 +4056,10 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4314,10 +4314,10 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.13</v>
+        <v>4.1</v>
       </c>
       <c r="M34" t="n">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.91</v>
+        <v>1.69</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="M35" t="n">
-        <v>3.06</v>
+        <v>3.21</v>
       </c>
       <c r="N35" t="n">
-        <v>3.61</v>
+        <v>2.79</v>
       </c>
       <c r="O35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.1</v>
+        <v>1.92</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="N36" t="n">
-        <v>1.69</v>
+        <v>3.14</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>3.95</v>
+        <v>3.28</v>
       </c>
       <c r="N37" t="n">
-        <v>4.6</v>
+        <v>3.19</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.34</v>
+        <v>1.68</v>
       </c>
       <c r="M38" t="n">
-        <v>3.01</v>
+        <v>3.74</v>
       </c>
       <c r="N38" t="n">
-        <v>2.78</v>
+        <v>3.89</v>
       </c>
       <c r="O38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z38" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z38" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AA38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="M39" t="n">
-        <v>3.21</v>
+        <v>3.06</v>
       </c>
       <c r="N39" t="n">
-        <v>2.79</v>
+        <v>3.61</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.68</v>
+        <v>2.75</v>
       </c>
       <c r="M40" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="N40" t="n">
-        <v>3.89</v>
+        <v>2.35</v>
       </c>
       <c r="O40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>3.01</v>
       </c>
       <c r="N41" t="n">
-        <v>2.35</v>
+        <v>2.78</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="M45" t="n">
-        <v>3.28</v>
+        <v>3.95</v>
       </c>
       <c r="N45" t="n">
-        <v>3.19</v>
+        <v>4.6</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7422,10 +7422,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="M58" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="N58" t="n">
-        <v>3.6</v>
+        <v>2.86</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="M64" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.15</v>
+        <v>1.25</v>
       </c>
       <c r="M65" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N65" t="n">
-        <v>3.2</v>
+        <v>16</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="M67" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N67" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N68" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,7 +9222,7 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z68" t="n">
         <v>1.55</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.6</v>
+        <v>1.32</v>
       </c>
       <c r="M73" t="n">
-        <v>2.61</v>
+        <v>4.3</v>
       </c>
       <c r="N73" t="n">
-        <v>2.84</v>
+        <v>7.8</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9861,16 +9861,16 @@
         <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
       <c r="M74" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="N74" t="n">
-        <v>7.8</v>
+        <v>2.84</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9990,16 +9990,16 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,16 +2256,16 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,16 +2643,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.75</v>
+        <v>2.74</v>
       </c>
       <c r="M25" t="n">
-        <v>3.83</v>
+        <v>3.23</v>
       </c>
       <c r="N25" t="n">
-        <v>3.47</v>
+        <v>2.24</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.16</v>
+        <v>3.28</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4056,10 +4056,10 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.8</v>
+        <v>1.92</v>
       </c>
       <c r="M30" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>2.85</v>
+        <v>3.91</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4314,16 +4314,16 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N34" t="n">
-        <v>1.69</v>
+        <v>3.19</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.92</v>
+        <v>2.75</v>
       </c>
       <c r="M36" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>3.14</v>
+        <v>2.35</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="M37" t="n">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="N37" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB37" t="n">
         <v>1.65</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="M38" t="n">
-        <v>3.74</v>
+        <v>3.95</v>
       </c>
       <c r="N38" t="n">
-        <v>3.89</v>
+        <v>4.6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.94</v>
+        <v>4.1</v>
       </c>
       <c r="M39" t="n">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>3.61</v>
+        <v>1.69</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.75</v>
+        <v>2.22</v>
       </c>
       <c r="M40" t="n">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="N40" t="n">
-        <v>2.35</v>
+        <v>2.79</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5709,34 +5709,34 @@
         <v>2.78</v>
       </c>
       <c r="O41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>2.2</v>
@@ -5745,16 +5745,16 @@
         <v>1.6</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="M42" t="n">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="N42" t="n">
-        <v>2.61</v>
+        <v>3.89</v>
       </c>
       <c r="O42" t="n">
-        <v>2.97</v>
+        <v>2.25</v>
       </c>
       <c r="P42" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T42" t="n">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="U42" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="V42" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W42" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="X42" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.03</v>
+        <v>2.36</v>
       </c>
       <c r="M44" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="N44" t="n">
-        <v>3.1</v>
+        <v>2.61</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.54</v>
+        <v>1.94</v>
       </c>
       <c r="M45" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q45" t="n">
         <v>3.95</v>
       </c>
-      <c r="N45" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.07</v>
+        <v>2.7</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7422,10 +7422,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,16 +7573,16 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45894.63541666666</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,16 +7831,16 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45894.63541666666</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N65" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O65" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P65" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R65" t="n">
         <v>1.25</v>
       </c>
-      <c r="M65" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N65" t="n">
-        <v>16</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y65" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,16 +8863,16 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI65" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45894.66666666666</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,61 +8925,61 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="M66" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N66" t="n">
-        <v>1.92</v>
+        <v>4</v>
       </c>
       <c r="O66" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.35</v>
+        <v>1.55</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -8992,16 +8992,16 @@
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI66" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AJ66" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45894.66666666666</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="M67" t="n">
         <v>3.1</v>
       </c>
       <c r="N67" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.15</v>
+        <v>1.25</v>
       </c>
       <c r="M68" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N68" t="n">
-        <v>3.2</v>
+        <v>16</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.13</v>
+        <v>1.87</v>
       </c>
       <c r="M75" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N75" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10119,16 +10119,16 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.87</v>
+        <v>2.13</v>
       </c>
       <c r="M76" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N76" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10248,16 +10248,16 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>

--- a/jogos_2025-08-25.xlsx
+++ b/jogos_2025-08-25.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>9.5</v>
+        <v>2.88</v>
       </c>
       <c r="M12" t="n">
-        <v>4.2</v>
+        <v>2.57</v>
       </c>
       <c r="N12" t="n">
-        <v>1.34</v>
+        <v>2.6</v>
       </c>
       <c r="O12" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,16 +2379,16 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.65</v>
+        <v>8.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="N17" t="n">
-        <v>1.73</v>
+        <v>1.32</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.26</v>
+        <v>1.77</v>
       </c>
       <c r="AA17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.35</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="M24" t="n">
-        <v>3.83</v>
+        <v>3.11</v>
       </c>
       <c r="N24" t="n">
-        <v>3.47</v>
+        <v>3.02</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.74</v>
+        <v>1.75</v>
       </c>
       <c r="M25" t="n">
-        <v>3.23</v>
+        <v>3.83</v>
       </c>
       <c r="N25" t="n">
-        <v>2.24</v>
+        <v>3.47</v>
       </c>
       <c r="O25" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.28</v>
+        <v>2.16</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P26" t="n">
         <v>2.14</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.8</v>
+        <v>1.92</v>
       </c>
       <c r="M28" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>2.85</v>
+        <v>3.91</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="X28" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y28" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="N29" t="n">
-        <v>4.1</v>
+        <v>2.85</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4185,16 +4185,16 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Z30" t="n">
         <v>1.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="N33" t="n">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="M34" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>3.19</v>
+        <v>2.35</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>3.27</v>
       </c>
       <c r="N36" t="n">
-        <v>2.35</v>
+        <v>2.91</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,62 +5184,62 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="M37" t="n">
-        <v>3.58</v>
+        <v>3.06</v>
       </c>
       <c r="N37" t="n">
-        <v>3.14</v>
+        <v>3.61</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AA37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD37" t="n">
         <v>2.25</v>
       </c>
-      <c r="AB37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
       <c r="AE37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.1</v>
+        <v>1.92</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="N39" t="n">
-        <v>1.69</v>
+        <v>3.14</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.22</v>
+        <v>2.03</v>
       </c>
       <c r="M40" t="n">
-        <v>3.21</v>
+        <v>3.29</v>
       </c>
       <c r="N40" t="n">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="M41" t="n">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="N41" t="n">
-        <v>2.78</v>
+        <v>2.61</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.68</v>
+        <v>4.1</v>
       </c>
       <c r="M42" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>3.89</v>
+        <v>1.69</v>
       </c>
       <c r="O42" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P42" t="n">
         <v>2.25</v>
       </c>
-      <c r="P42" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>2.16</v>
       </c>
       <c r="R42" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="S42" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="T42" t="n">
-        <v>2.31</v>
+        <v>2.66</v>
       </c>
       <c r="U42" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W42" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X42" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.25</v>
+        <v>2.09</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.85</v>
+        <v>1.15</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="M43" t="n">
-        <v>3.29</v>
+        <v>3.21</v>
       </c>
       <c r="N43" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="M44" t="n">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="N44" t="n">
-        <v>2.61</v>
+        <v>3.89</v>
       </c>
       <c r="O44" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.94</v>
+        <v>2.34</v>
       </c>
       <c r="M45" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="N45" t="n">
-        <v>3.61</v>
+        <v>2.78</v>
       </c>
       <c r="O45" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q45" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X45" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.68</v>
-      </c>
       <c r="Z45" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6483,34 +6483,34 @@
         <v>2.74</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y47" t="n">
         <v>1.8</v>
@@ -6519,16 +6519,16 @@
         <v>1.9</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7422,10 +7422,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,16 +7573,16 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45894.63541666666</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,16 +7831,16 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45894.63541666666</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.22</v>
+        <v>2.49</v>
       </c>
       <c r="M58" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3</v>
+      </c>
+      <c r="P58" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q58" t="n">
         <v>3.3</v>
       </c>
-      <c r="N58" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.19</v>
+        <v>1.72</v>
       </c>
       <c r="M60" t="n">
-        <v>2.98</v>
+        <v>3.8</v>
       </c>
       <c r="N60" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.45</v>
+        <v>1.43</v>
       </c>
       <c r="M62" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="N62" t="n">
-        <v>1.96</v>
+        <v>6.8</v>
       </c>
       <c r="O62" t="n">
-        <v>4.33</v>
+        <v>1.89</v>
       </c>
       <c r="P62" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.75</v>
+        <v>6.5</v>
       </c>
       <c r="R62" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S62" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X62" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AB62" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S62" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T62" t="n">
-        <v>3</v>
-      </c>
-      <c r="U62" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>1.83</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,16 +8476,16 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI62" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
         <v>45894.65625</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,34 +8538,34 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.43</v>
+        <v>3.45</v>
       </c>
       <c r="M63" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="N63" t="n">
-        <v>6.8</v>
+        <v>1.96</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
@@ -8577,11 +8577,11 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z63" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z63" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AA63" t="n">
         <v>0</v>
       </c>
@@ -8589,10 +8589,10 @@
         <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8611,10 +8611,10 @@
         <v>0</v>
       </c>
       <c r="AI63" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45894.65625</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,62 +8667,62 @@
         </is>
       </c>
       <c r="L64" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M64" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N64" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O64" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P64" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S64" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X64" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD64" t="n">
         <v>2.4</v>
       </c>
-      <c r="M64" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N64" t="n">
-        <v>3</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>0</v>
-      </c>
       <c r="AE64" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8734,16 +8734,16 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI64" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45894.66666666666</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="M65" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="N65" t="n">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="O65" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z65" t="n">
         <v>1.65</v>
       </c>
-      <c r="V65" t="n">
-        <v>1</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X65" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AA65" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,16 +8863,16 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AJ65" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45894.66666666666</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,14 +8925,14 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="M66" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N66" t="n">
         <v>3.25</v>
       </c>
-      <c r="N66" t="n">
-        <v>4</v>
-      </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
@@ -8964,7 +8964,7 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z66" t="n">
         <v>1.55</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.15</v>
+        <v>1.25</v>
       </c>
       <c r="M67" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N67" t="n">
-        <v>3.2</v>
+        <v>16</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="M68" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>202